--- a/Aii竞彩数据总表.xlsx
+++ b/Aii竞彩数据总表.xlsx
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU138"/>
+  <dimension ref="A1:AU168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11071,11 +11071,821 @@
         <v>0</v>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>威廉二世</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>瓦尔韦克</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>塞维利亚</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>西班牙人</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>富勒姆</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>伯恩茅斯</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>桑德兰</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>曼联</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>莱红牛</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>圣保利</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>斯图加特</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>勒沃库森</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>霍芬海姆</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>不来梅</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>奥格斯堡</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>门兴</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>哥德堡</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>哈马比</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>代格福什</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>米亚尔比</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>卡利亚里</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>乌迪内斯</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>国际图尔</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>雅罗</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>萨普斯堡</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>腓特烈</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>埃尔切</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>阿拉维斯</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>米堡</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>南安普敦</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>利物浦</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>切尔西</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>波鸿</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>汉诺威96</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>大田市民</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>浦项制铁</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>光州FC</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>江原FC</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>大阪樱花</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>长崎航海</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>奥克兰FC</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>阿德莱德</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>莱万特</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>奥萨苏纳</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>赫尔城</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>米尔沃尔</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>朗斯</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>南特</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>都灵</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>萨索洛</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>多特蒙德</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>法兰克福</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>库奥皮奥</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>塞伊奈</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>汉坎</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>瓦勒伦加</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>埃夫斯堡</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>布鲁马波</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>凯泽</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>比勒费</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:V50"/>
   <mergeCells count="4">
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:N1"/>
-    <mergeCell ref="A1:F1"/>
     <mergeCell ref="T1:V1"/>
     <mergeCell ref="O1:S1"/>
   </mergeCells>

--- a/Aii竞彩数据总表.xlsx
+++ b/Aii竞彩数据总表.xlsx
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU168"/>
+  <dimension ref="A1:AU199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11881,11 +11881,1131 @@
         </is>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>威廉二世</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>瓦尔韦克</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>荷兰乙级联赛</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>塞维利亚</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>西班牙人</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>西班牙甲级联赛</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>富勒姆</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>伯恩茅斯</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>英格兰超级联赛</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>桑德兰</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>曼联</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>英格兰超级联赛</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>莱红牛</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>圣保利</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>斯图加特</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>勒沃库森</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>霍芬海姆</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>不来梅</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>奥格斯堡</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>门兴</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>哥德堡</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>哈马比</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>瑞典超级联赛</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>代格福什</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>米亚尔比</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>瑞典超级联赛</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>卡利亚里</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>乌迪内斯</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>意大利甲级联赛</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>国际图尔</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>雅罗</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>芬兰超级联赛</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>萨普斯堡</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>腓特烈</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>挪威超级联赛</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>埃尔切</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>阿拉维斯</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>西班牙甲级联赛</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>米堡</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>南安普敦</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>英格兰冠军联赛</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>利物浦</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>切尔西</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>英格兰超级联赛</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>波鸿</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>汉诺威96</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>德国乙级联赛</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>大田市民</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>浦项制铁</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>韩国职业联赛</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>光州FC</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>江原FC</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>韩国职业联赛</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>大阪樱花</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>长崎航海</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>日本职业联赛</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>奥克兰FC</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>阿德莱德</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>澳大利亚超级联赛</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>莱万特</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>奥萨苏纳</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>西班牙甲级联赛</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="H190" t="n">
+        <v>3</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>赫尔城</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>米尔沃尔</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>英格兰冠军联赛</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="H191" t="n">
+        <v>3</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>朗斯</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>南特</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>法国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>胜-胜</t>
+        </is>
+      </c>
+      <c r="H192" t="n">
+        <v>4</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>都灵</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>萨索洛</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>意大利甲级联赛</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="H193" t="n">
+        <v>3</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>多特蒙德</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>法兰克福</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>胜-胜</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
+        <v>5</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>库奥皮奥</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>塞伊奈</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>芬兰超级联赛</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>汉坎</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>瓦勒伦加</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>挪威超级联赛</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="H196" t="n">
+        <v>3</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>埃夫斯堡</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>布鲁马波</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>瑞典超级联赛</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>凯泽</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>比勒费</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>德国乙级联赛</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>帕德博恩</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>卡斯鲁厄</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>德国乙级联赛</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:V50"/>
   <mergeCells count="4">
+    <mergeCell ref="G1:N1"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:N1"/>
     <mergeCell ref="T1:V1"/>
     <mergeCell ref="O1:S1"/>
   </mergeCells>

--- a/Aii竞彩数据总表.xlsx
+++ b/Aii竞彩数据总表.xlsx
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU199"/>
+  <dimension ref="A1:AU230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11907,8 +11907,6 @@
           <t>荷兰乙级联赛</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
       <c r="O169" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -11941,8 +11939,6 @@
           <t>西班牙甲级联赛</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
       <c r="O170" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -11975,8 +11971,6 @@
           <t>英格兰超级联赛</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
       <c r="O171" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12009,8 +12003,6 @@
           <t>英格兰超级联赛</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
       <c r="O172" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12043,8 +12035,6 @@
           <t>德国甲级联赛</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
       <c r="O173" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12077,8 +12067,6 @@
           <t>德国甲级联赛</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
       <c r="O174" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12111,8 +12099,6 @@
           <t>德国甲级联赛</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
       <c r="O175" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12145,8 +12131,6 @@
           <t>德国甲级联赛</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
       <c r="O176" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12179,8 +12163,6 @@
           <t>瑞典超级联赛</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
       <c r="O177" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12213,8 +12195,6 @@
           <t>瑞典超级联赛</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
       <c r="O178" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12247,8 +12227,6 @@
           <t>意大利甲级联赛</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
       <c r="O179" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12281,8 +12259,6 @@
           <t>芬兰超级联赛</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
       <c r="O180" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12315,8 +12291,6 @@
           <t>挪威超级联赛</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
       <c r="O181" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12349,8 +12323,6 @@
           <t>西班牙甲级联赛</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
       <c r="O182" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12383,8 +12355,6 @@
           <t>英格兰冠军联赛</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
       <c r="O183" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12417,8 +12387,6 @@
           <t>英格兰超级联赛</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
       <c r="O184" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12451,8 +12419,6 @@
           <t>德国乙级联赛</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
       <c r="O185" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12485,8 +12451,6 @@
           <t>韩国职业联赛</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
       <c r="O186" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12519,8 +12483,6 @@
           <t>韩国职业联赛</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
       <c r="O187" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12553,8 +12515,6 @@
           <t>日本职业联赛</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
       <c r="O188" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12587,8 +12547,6 @@
           <t>澳大利亚超级联赛</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
       <c r="O189" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12846,8 +12804,6 @@
           <t>芬兰超级联赛</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
-      <c r="H195" t="inlineStr"/>
       <c r="O195" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12925,8 +12881,6 @@
           <t>瑞典超级联赛</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr"/>
-      <c r="H197" t="inlineStr"/>
       <c r="O197" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12959,8 +12913,6 @@
           <t>德国乙级联赛</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr"/>
-      <c r="H198" t="inlineStr"/>
       <c r="O198" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -12993,9 +12945,1127 @@
           <t>德国乙级联赛</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr"/>
       <c r="O199" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>威廉二世</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>瓦尔韦克</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>荷兰乙级联赛</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>塞维利亚</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>西班牙人</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>西班牙甲级联赛</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>富勒姆</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>伯恩茅斯</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>英格兰超级联赛</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>桑德兰</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>曼联</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>英格兰超级联赛</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>莱红牛</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>圣保利</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>斯图加特</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>勒沃库森</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>霍芬海姆</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>不来梅</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>奥格斯堡</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>门兴</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>哥德堡</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>哈马比</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>瑞典超级联赛</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>代格福什</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>米亚尔比</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>瑞典超级联赛</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>卡利亚里</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>乌迪内斯</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>意大利甲级联赛</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>国际图尔</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>雅罗</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>芬兰超级联赛</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>萨普斯堡</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>腓特烈</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>挪威超级联赛</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>埃尔切</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>阿拉维斯</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>西班牙甲级联赛</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>米堡</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>南安普敦</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>英格兰冠军联赛</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>利物浦</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>切尔西</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>英格兰超级联赛</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>波鸿</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>汉诺威96</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>德国乙级联赛</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>大田市民</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>浦项制铁</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>韩国职业联赛</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>光州FC</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>江原FC</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>韩国职业联赛</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>大阪樱花</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>长崎航海</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>日本职业联赛</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>奥克兰FC</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>阿德莱德</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>澳大利亚超级联赛</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>莱万特</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>奥萨苏纳</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>西班牙甲级联赛</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="H221" t="n">
+        <v>3</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>赫尔城</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>米尔沃尔</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>英格兰冠军联赛</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="H222" t="n">
+        <v>3</v>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>朗斯</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>南特</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>法国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>胜-胜</t>
+        </is>
+      </c>
+      <c r="H223" t="n">
+        <v>4</v>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>都灵</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>萨索洛</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>意大利甲级联赛</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="H224" t="n">
+        <v>3</v>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>多特蒙德</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>法兰克福</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>胜-胜</t>
+        </is>
+      </c>
+      <c r="H225" t="n">
+        <v>5</v>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>库奥皮奥</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>塞伊奈</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>芬兰超级联赛</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>汉坎</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>瓦勒伦加</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>挪威超级联赛</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="H227" t="n">
+        <v>3</v>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>埃夫斯堡</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>布鲁马波</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>瑞典超级联赛</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>凯泽</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>比勒费</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>德国乙级联赛</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>帕德博恩</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>卡斯鲁厄</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>德国乙级联赛</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+      <c r="O230" t="inlineStr">
         <is>
           <t>待结算</t>
         </is>
@@ -13004,9 +14074,9 @@
   </sheetData>
   <autoFilter ref="A1:V50"/>
   <mergeCells count="4">
+    <mergeCell ref="T1:V1"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:N1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="T1:V1"/>
     <mergeCell ref="O1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Aii竞彩数据总表.xlsx
+++ b/Aii竞彩数据总表.xlsx
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU230"/>
+  <dimension ref="A1:AU261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12977,8 +12977,6 @@
           <t>荷兰乙级联赛</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
       <c r="O200" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13011,8 +13009,6 @@
           <t>西班牙甲级联赛</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr"/>
       <c r="O201" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13045,8 +13041,6 @@
           <t>英格兰超级联赛</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr"/>
       <c r="O202" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13079,8 +13073,6 @@
           <t>英格兰超级联赛</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr"/>
       <c r="O203" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13113,8 +13105,6 @@
           <t>德国甲级联赛</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr"/>
       <c r="O204" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13147,8 +13137,6 @@
           <t>德国甲级联赛</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr"/>
-      <c r="H205" t="inlineStr"/>
       <c r="O205" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13181,8 +13169,6 @@
           <t>德国甲级联赛</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr"/>
-      <c r="H206" t="inlineStr"/>
       <c r="O206" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13215,8 +13201,6 @@
           <t>德国甲级联赛</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr"/>
-      <c r="H207" t="inlineStr"/>
       <c r="O207" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13249,8 +13233,6 @@
           <t>瑞典超级联赛</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr"/>
       <c r="O208" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13283,8 +13265,6 @@
           <t>瑞典超级联赛</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr"/>
-      <c r="H209" t="inlineStr"/>
       <c r="O209" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13317,8 +13297,6 @@
           <t>意大利甲级联赛</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr"/>
-      <c r="H210" t="inlineStr"/>
       <c r="O210" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13351,8 +13329,6 @@
           <t>芬兰超级联赛</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr"/>
-      <c r="H211" t="inlineStr"/>
       <c r="O211" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13385,8 +13361,6 @@
           <t>挪威超级联赛</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr"/>
-      <c r="H212" t="inlineStr"/>
       <c r="O212" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13419,8 +13393,6 @@
           <t>西班牙甲级联赛</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr"/>
-      <c r="H213" t="inlineStr"/>
       <c r="O213" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13453,8 +13425,6 @@
           <t>英格兰冠军联赛</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr"/>
-      <c r="H214" t="inlineStr"/>
       <c r="O214" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13487,8 +13457,6 @@
           <t>英格兰超级联赛</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr"/>
-      <c r="H215" t="inlineStr"/>
       <c r="O215" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13521,8 +13489,6 @@
           <t>德国乙级联赛</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr"/>
       <c r="O216" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13555,8 +13521,6 @@
           <t>韩国职业联赛</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr"/>
-      <c r="H217" t="inlineStr"/>
       <c r="O217" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13589,8 +13553,6 @@
           <t>韩国职业联赛</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr"/>
-      <c r="H218" t="inlineStr"/>
       <c r="O218" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13623,8 +13585,6 @@
           <t>日本职业联赛</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="inlineStr"/>
       <c r="O219" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13657,8 +13617,6 @@
           <t>澳大利亚超级联赛</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr"/>
-      <c r="H220" t="inlineStr"/>
       <c r="O220" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13916,8 +13874,6 @@
           <t>芬兰超级联赛</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr"/>
-      <c r="H226" t="inlineStr"/>
       <c r="O226" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -13995,8 +13951,6 @@
           <t>瑞典超级联赛</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr"/>
-      <c r="H228" t="inlineStr"/>
       <c r="O228" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -14029,8 +13983,6 @@
           <t>德国乙级联赛</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr"/>
-      <c r="H229" t="inlineStr"/>
       <c r="O229" t="inlineStr">
         <is>
           <t>待结算</t>
@@ -14063,9 +14015,1127 @@
           <t>德国乙级联赛</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr"/>
-      <c r="H230" t="inlineStr"/>
       <c r="O230" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>威廉二世</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>瓦尔韦克</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>荷兰乙级联赛</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>塞维利亚</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>西班牙人</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>西班牙甲级联赛</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>富勒姆</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>伯恩茅斯</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>英格兰超级联赛</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>桑德兰</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>曼联</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>英格兰超级联赛</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>莱红牛</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>圣保利</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>斯图加特</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>勒沃库森</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>霍芬海姆</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>不来梅</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>奥格斯堡</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>门兴</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>哥德堡</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>哈马比</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>瑞典超级联赛</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>代格福什</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>米亚尔比</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>瑞典超级联赛</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>卡利亚里</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>乌迪内斯</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>意大利甲级联赛</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>国际图尔</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>雅罗</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>芬兰超级联赛</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>萨普斯堡</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>腓特烈</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>挪威超级联赛</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>埃尔切</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>阿拉维斯</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>西班牙甲级联赛</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>米堡</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>南安普敦</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>英格兰冠军联赛</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr"/>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>利物浦</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>切尔西</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>英格兰超级联赛</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>波鸿</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>汉诺威96</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>德国乙级联赛</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr"/>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>大田市民</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>浦项制铁</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>韩国职业联赛</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr"/>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>光州FC</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>江原FC</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>韩国职业联赛</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr"/>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>大阪樱花</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>长崎航海</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>日本职业联赛</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr"/>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>奥克兰FC</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>阿德莱德</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>澳大利亚超级联赛</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>莱万特</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>奥萨苏纳</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>西班牙甲级联赛</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="H252" t="n">
+        <v>3</v>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>赫尔城</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>米尔沃尔</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>英格兰冠军联赛</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="H253" t="n">
+        <v>3</v>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>朗斯</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>南特</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>法国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>胜-胜</t>
+        </is>
+      </c>
+      <c r="H254" t="n">
+        <v>4</v>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>都灵</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>萨索洛</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>意大利甲级联赛</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="H255" t="n">
+        <v>3</v>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>多特蒙德</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>法兰克福</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>胜-胜</t>
+        </is>
+      </c>
+      <c r="H256" t="n">
+        <v>5</v>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>库奥皮奥</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>塞伊奈</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>芬兰超级联赛</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>汉坎</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>瓦勒伦加</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>挪威超级联赛</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="H258" t="n">
+        <v>3</v>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>埃夫斯堡</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>布鲁马波</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>瑞典超级联赛</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr"/>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>凯泽</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>比勒费</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>德国乙级联赛</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr"/>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>待结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>帕德博恩</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>卡斯鲁厄</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>德国乙级联赛</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr"/>
+      <c r="O261" t="inlineStr">
         <is>
           <t>待结算</t>
         </is>
@@ -14074,9 +15144,9 @@
   </sheetData>
   <autoFilter ref="A1:V50"/>
   <mergeCells count="4">
-    <mergeCell ref="T1:V1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:N1"/>
+    <mergeCell ref="T1:V1"/>
     <mergeCell ref="O1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Aii竞彩数据总表.xlsx
+++ b/Aii竞彩数据总表.xlsx
@@ -669,8 +669,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU261"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:AU138"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
@@ -8312,6 +8312,50 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>澳超</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>周六001</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>奥克兰FC</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>阿德莱德</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M79" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N79" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="Y79" t="n">
         <v>4.1</v>
       </c>
@@ -8328,6 +8372,50 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>日职</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>周六002</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>大阪樱花</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>长崎航海</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M80" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N80" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="Y80" t="n">
         <v>3.25</v>
       </c>
@@ -8344,6 +8432,50 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>韩职</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>周六003</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>光州FC</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>江原FC</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="M81" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="N81" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
       <c r="Y81" t="n">
         <v>2.7</v>
       </c>
@@ -8360,6 +8492,50 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>韩职</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>周六004</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>大田市民</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>浦项制铁</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M82" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N82" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="Y82" t="n">
         <v>4.5</v>
       </c>
@@ -8376,6 +8552,50 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>德乙</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>周六005</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>波鸿</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>汉诺威96</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="M83" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N83" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
       <c r="Y83" t="n">
         <v>1.75</v>
       </c>
@@ -8392,6 +8612,50 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>英超</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>周六006</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>利物浦</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>切尔西</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M84" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N84" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="Y84" t="n">
         <v>3.1</v>
       </c>
@@ -8408,6 +8672,50 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>英冠</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>周六007</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>米堡</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>南安普敦</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M85" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N85" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="Y85" t="n">
         <v>4.22</v>
       </c>
@@ -8424,6 +8732,50 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>周六008</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>埃尔切</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>阿拉维斯</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M86" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N86" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="Y86" t="n">
         <v>4.45</v>
       </c>
@@ -8440,6 +8792,50 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>挪超</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>周六009</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>萨普斯堡</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>腓特烈</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M87" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N87" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="Y87" t="n">
         <v>3.48</v>
       </c>
@@ -8456,6 +8852,50 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>芬超</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>周六010</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>国际图尔</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>雅罗</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M88" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N88" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="Y88" t="n">
         <v>2.38</v>
       </c>
@@ -8472,6 +8912,50 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>意甲</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>周六011</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>卡利亚里</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>乌迪内斯</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M89" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N89" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="Y89" t="n">
         <v>5.7</v>
       </c>
@@ -8488,6 +8972,50 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>瑞超</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>周六012</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>代格福什</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>米亚尔比</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="M90" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N90" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
       <c r="Y90" t="n">
         <v>1.68</v>
       </c>
@@ -8504,6 +9032,50 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>瑞超</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>周六013</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>哥德堡</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>哈马比</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="M91" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N91" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
       <c r="Y91" t="n">
         <v>2.08</v>
       </c>
@@ -8520,6 +9092,50 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>周六014</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>奥格斯堡</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>门兴</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M92" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N92" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="Y92" t="n">
         <v>3.47</v>
       </c>
@@ -8536,6 +9152,50 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>周六015</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>霍芬海姆</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>不来梅</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M93" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="N93" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="Y93" t="n">
         <v>1.99</v>
       </c>
@@ -8552,6 +9212,50 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>周六016</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>斯图加特</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>勒沃库森</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M94" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N94" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="Y94" t="n">
         <v>3.92</v>
       </c>
@@ -8568,6 +9272,50 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>周六017</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>莱红牛</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>圣保利</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M95" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N95" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
       <c r="Y95" t="n">
         <v>2.81</v>
       </c>
@@ -8584,6 +9332,50 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>英超</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>周六018</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>桑德兰</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>曼联</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="M96" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N96" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
       <c r="Y96" t="n">
         <v>1.85</v>
       </c>
@@ -8600,6 +9392,50 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>英超</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>周六019</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>富勒姆</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>伯恩茅斯</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M97" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N97" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
       <c r="Y97" t="n">
         <v>1.5</v>
       </c>
@@ -8616,6 +9452,50 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>周六020</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>塞维利亚</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>西班牙人</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M98" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N98" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="Y98" t="n">
         <v>4.22</v>
       </c>
@@ -8632,6 +9512,50 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>荷乙</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>周六021</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>威廉二世</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>瓦尔韦克</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M99" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N99" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="Y99" t="n">
         <v>3.65</v>
       </c>
@@ -8648,6 +9572,50 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>意甲</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>周六022</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>拉齐奥</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>国际米兰</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M100" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N100" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
       <c r="Y100" t="n">
         <v>1.92</v>
       </c>
@@ -8664,6 +9632,50 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>英超</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>周六023</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>曼城</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>布伦特</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M101" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N101" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="Y101" t="n">
         <v>1.77</v>
       </c>
@@ -8680,6 +9692,50 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>周六024</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>沃夫斯堡</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>拜仁</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="M102" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N102" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
       <c r="Y102" t="n">
         <v>2.32</v>
       </c>
@@ -8696,6 +9752,50 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>周六025</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>马竞</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>塞尔塔</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M103" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N103" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="Y103" t="n">
         <v>3.9</v>
       </c>
@@ -8712,6 +9812,50 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>美职</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>周六026</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>多伦多</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>迈国际</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="M104" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="N104" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
       <c r="Y104" t="n">
         <v>2.01</v>
       </c>
@@ -8728,6 +9872,50 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>沙职</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>周六027</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>迈季宽广</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>胡巴卡德</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="M105" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="N105" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
       <c r="Y105" t="n">
         <v>2.68</v>
       </c>
@@ -8744,6 +9932,50 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>法乙</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>周六028</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>阿纳西</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>罗德兹</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M106" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N106" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="Y106" t="n">
         <v>4.3</v>
       </c>
@@ -8760,6 +9992,50 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>意甲</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>周六029</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>莱切</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>尤文图斯</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="M107" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="N107" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
       <c r="Y107" t="n">
         <v>2.73</v>
       </c>
@@ -8776,6 +10052,50 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>周六030</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>皇家社会</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>贝蒂斯</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M108" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N108" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="Y108" t="n">
         <v>5</v>
       </c>
@@ -8794,88 +10114,63 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>澳超</t>
+          <t>韩职</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>周六001</t>
+          <t>周日001</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>奥克兰FC</t>
+          <t>蔚山现代</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>阿德莱德</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>小2.5</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>防2-0</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
+          <t>富川FC</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>1.53</v>
       </c>
       <c r="M109" t="n">
-        <v>2</v>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>+6%</t>
-        </is>
-      </c>
-      <c r="W109" t="n">
-        <v>0</v>
-      </c>
-      <c r="X109" t="n">
-        <v>0</v>
+        <v>3.55</v>
+      </c>
+      <c r="N109" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -8885,909 +10180,609 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>周六002</t>
+          <t>周日002</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>大阪樱花</t>
+          <t>大阪钢巴</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>长崎航海</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>小2.5</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>防1-0</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
+          <t>广岛三箭</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>3.12</v>
       </c>
       <c r="M110" t="n">
-        <v>2</v>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>+12%</t>
-        </is>
-      </c>
-      <c r="W110" t="n">
-        <v>0</v>
-      </c>
-      <c r="X110" t="n">
-        <v>0</v>
+        <v>3.35</v>
+      </c>
+      <c r="N110" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>韩职</t>
+          <t>日职</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>周六003</t>
+          <t>周日003</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>光州FC</t>
+          <t>柏太阳神</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>江原FC</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>负-负</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>小2.5</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>防0-2</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
+          <t>川崎前锋</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>1.93</v>
       </c>
       <c r="M111" t="n">
-        <v>2</v>
-      </c>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>+14%</t>
-        </is>
-      </c>
-      <c r="W111" t="n">
-        <v>0</v>
-      </c>
-      <c r="X111" t="n">
-        <v>0</v>
+        <v>3.4</v>
+      </c>
+      <c r="N111" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>韩职</t>
+          <t>日职</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>周六004</t>
+          <t>周日004</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>大田市民</t>
+          <t>千叶市原</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>浦项制铁</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>小2.5</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>防2-0</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
+          <t>町田泽维</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>4.5</v>
       </c>
       <c r="M112" t="n">
-        <v>2</v>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>+4%</t>
-        </is>
-      </c>
-      <c r="W112" t="n">
-        <v>0</v>
-      </c>
-      <c r="X112" t="n">
-        <v>0</v>
+        <v>3.45</v>
+      </c>
+      <c r="N112" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>德乙</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>周六005</t>
+          <t>周日005</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>波鸿</t>
+          <t>维罗纳</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>汉诺威96</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>负-负</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>大2.5</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>防1-3</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
+          <t>科莫</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>8.25</v>
       </c>
       <c r="M113" t="n">
-        <v>2</v>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>+11%</t>
-        </is>
-      </c>
-      <c r="W113" t="n">
-        <v>0</v>
-      </c>
-      <c r="X113" t="n">
-        <v>0</v>
+        <v>4.65</v>
+      </c>
+      <c r="N113" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>英超</t>
+          <t>德乙</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>周六006</t>
+          <t>周日006</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>利物浦</t>
+          <t>杜塞多夫</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>切尔西</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>大2.5</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>防3-1</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
+          <t>埃沃斯堡</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>3.02</v>
       </c>
       <c r="M114" t="n">
-        <v>2</v>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>+10%</t>
-        </is>
-      </c>
-      <c r="W114" t="n">
-        <v>0</v>
-      </c>
-      <c r="X114" t="n">
-        <v>0</v>
+        <v>3.72</v>
+      </c>
+      <c r="N114" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>英冠</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>周六007</t>
+          <t>周日007</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>米堡</t>
+          <t>马洛卡</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>南安普敦</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>大2.5</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>防2-1</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
+          <t>比利亚雷</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>2.15</v>
       </c>
       <c r="M115" t="n">
-        <v>2</v>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>+5%</t>
-        </is>
-      </c>
-      <c r="W115" t="n">
-        <v>0</v>
-      </c>
-      <c r="X115" t="n">
-        <v>0</v>
+        <v>3.4</v>
+      </c>
+      <c r="N115" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>挪超</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>周六008</t>
+          <t>周日008</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>埃尔切</t>
+          <t>罗森博格</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>阿拉维斯</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>大2.5</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>防2-2</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
+          <t>利勒斯特</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>2.52</v>
       </c>
       <c r="M116" t="n">
-        <v>2</v>
-      </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>+6%</t>
-        </is>
-      </c>
-      <c r="W116" t="n">
-        <v>0</v>
-      </c>
-      <c r="X116" t="n">
-        <v>0</v>
+        <v>3.45</v>
+      </c>
+      <c r="N116" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>挪超</t>
+          <t>英超</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>周六009</t>
+          <t>周日009</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>萨普斯堡</t>
+          <t>伯恩利</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>腓特烈</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>小2.5</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>防2-0</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
+          <t>维拉</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>4.95</v>
       </c>
       <c r="M117" t="n">
-        <v>2</v>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>+10%</t>
-        </is>
-      </c>
-      <c r="W117" t="n">
-        <v>0</v>
-      </c>
-      <c r="X117" t="n">
-        <v>0</v>
+        <v>3.9</v>
+      </c>
+      <c r="N117" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>芬超</t>
+          <t>英超</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>周六010</t>
+          <t>周日010</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>国际图尔</t>
+          <t>水晶宫</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>雅罗</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>小2.5</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>防1-0</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
+          <t>埃弗顿</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>2.65</v>
       </c>
       <c r="M118" t="n">
-        <v>2</v>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>+16%</t>
-        </is>
-      </c>
-      <c r="W118" t="n">
-        <v>0</v>
-      </c>
-      <c r="X118" t="n">
-        <v>0</v>
+        <v>3.15</v>
+      </c>
+      <c r="N118" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>英超</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>周六011</t>
+          <t>周日011</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>卡利亚里</t>
+          <t>诺丁汉</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>乌迪内斯</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>平局</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>2-2</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>平-平</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>大2.5</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>防1-2</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
+          <t>纽卡斯尔</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>2.57</v>
       </c>
       <c r="M119" t="n">
-        <v>2</v>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
-      <c r="W119" t="n">
-        <v>0</v>
-      </c>
-      <c r="X119" t="n">
-        <v>0</v>
+        <v>3.32</v>
+      </c>
+      <c r="N119" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>瑞超</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>周六012</t>
+          <t>周日012</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>代格福什</t>
+          <t>克雷莫纳</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>米亚尔比</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>平-负</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>小2.5</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>防1-1</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
+          <t>比萨</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>1.56</v>
       </c>
       <c r="M120" t="n">
-        <v>2</v>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>+7%</t>
-        </is>
-      </c>
-      <c r="W120" t="n">
-        <v>0</v>
-      </c>
-      <c r="X120" t="n">
-        <v>0</v>
+        <v>3.55</v>
+      </c>
+      <c r="N120" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>瑞超</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>周六013</t>
+          <t>周日013</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>哥德堡</t>
+          <t>佛罗伦萨</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>哈马比</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>负-负</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>小2.5</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>防0-2</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
+          <t>热那亚</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>1.89</v>
       </c>
       <c r="M121" t="n">
-        <v>2</v>
-      </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>+16%</t>
-        </is>
-      </c>
-      <c r="W121" t="n">
-        <v>0</v>
-      </c>
-      <c r="X121" t="n">
-        <v>0</v>
+        <v>3.15</v>
+      </c>
+      <c r="N121" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -9797,377 +10792,252 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>周六014</t>
+          <t>周日014</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>奥格斯堡</t>
+          <t>汉堡</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>门兴</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>3-2</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>大2.5</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>防2-3</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
+          <t>弗赖堡</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>2.46</v>
       </c>
       <c r="M122" t="n">
-        <v>2</v>
-      </c>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>+11%</t>
-        </is>
-      </c>
-      <c r="W122" t="n">
-        <v>0</v>
-      </c>
-      <c r="X122" t="n">
-        <v>0</v>
+        <v>3.45</v>
+      </c>
+      <c r="N122" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>德甲</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>周六015</t>
+          <t>周日015</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>霍芬海姆</t>
+          <t>毕尔巴鄂</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>不来梅</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>3-2</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>大2.5</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>防2-2</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
+          <t>巴伦西亚</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>1.6</v>
       </c>
       <c r="M123" t="n">
-        <v>2</v>
-      </c>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>+20%</t>
-        </is>
-      </c>
-      <c r="W123" t="n">
-        <v>0</v>
-      </c>
-      <c r="X123" t="n">
-        <v>0</v>
+        <v>3.5</v>
+      </c>
+      <c r="N123" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>德甲</t>
+          <t>荷甲</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>周六016</t>
+          <t>周日016</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>斯图加特</t>
+          <t>费耶诺德</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>勒沃库森</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>3-2</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>大2.5</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>防2-2</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
+          <t>阿尔克马</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>1.65</v>
       </c>
       <c r="M124" t="n">
-        <v>2</v>
-      </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>+8%</t>
-        </is>
-      </c>
-      <c r="W124" t="n">
-        <v>0</v>
-      </c>
-      <c r="X124" t="n">
-        <v>0</v>
+        <v>3.95</v>
+      </c>
+      <c r="N124" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>德甲</t>
+          <t>荷甲</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>周六017</t>
+          <t>周日017</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>莱红牛</t>
+          <t>阿贾克斯</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>圣保利</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>大2.5</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>⚠️让-2深盘·主胜可能不穿盘</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>9/10</t>
-        </is>
+          <t>乌德勒支</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>1.49</v>
       </c>
       <c r="M125" t="n">
-        <v>2</v>
-      </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>+24%</t>
-        </is>
-      </c>
-      <c r="W125" t="n">
-        <v>0</v>
-      </c>
-      <c r="X125" t="n">
-        <v>0</v>
+        <v>4.25</v>
+      </c>
+      <c r="N125" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>英超</t>
+          <t>荷甲</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>周六018</t>
+          <t>周日018</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>桑德兰</t>
+          <t>格罗宁根</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>曼联</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>负-负</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>大2.5</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>防2-1</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
+          <t>奈梅亨</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>2.74</v>
       </c>
       <c r="M126" t="n">
-        <v>2</v>
-      </c>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>+9%</t>
-        </is>
-      </c>
-      <c r="W126" t="n">
-        <v>0</v>
-      </c>
-      <c r="X126" t="n">
-        <v>0</v>
+        <v>3.65</v>
+      </c>
+      <c r="N126" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -10177,4967 +11047,588 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>周六019</t>
+          <t>周日019</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>富勒姆</t>
+          <t>西汉姆联</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>伯恩茅斯</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>1-3</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>负-负</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>大2.5</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>防1-2</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
+          <t>阿森纳</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>5.4</v>
       </c>
       <c r="M127" t="n">
-        <v>2</v>
-      </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t>+4%</t>
-        </is>
-      </c>
-      <c r="W127" t="n">
-        <v>0</v>
-      </c>
-      <c r="X127" t="n">
-        <v>0</v>
+        <v>4.1</v>
+      </c>
+      <c r="N127" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>德甲</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>周六020</t>
+          <t>周日020</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>塞维利亚</t>
+          <t>科隆</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>西班牙人</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>大2.5</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>防1-2</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
+          <t>海登海姆</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>1.9</v>
       </c>
       <c r="M128" t="n">
-        <v>2</v>
-      </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>+4%</t>
-        </is>
-      </c>
-      <c r="W128" t="n">
-        <v>0</v>
-      </c>
-      <c r="X128" t="n">
-        <v>0</v>
+        <v>3.75</v>
+      </c>
+      <c r="N128" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>荷乙</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>周六021</t>
+          <t>周日021</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>威廉二世</t>
+          <t>帕尔马</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>瓦尔韦克</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>小2.5</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>防1-0</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>6.25</v>
       </c>
       <c r="M129" t="n">
-        <v>2</v>
-      </c>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>+10%</t>
-        </is>
-      </c>
-      <c r="W129" t="n">
-        <v>0</v>
-      </c>
-      <c r="X129" t="n">
-        <v>0</v>
+        <v>4.1</v>
+      </c>
+      <c r="N129" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>周六022</t>
+          <t>周日022</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>拉齐奥</t>
+          <t>奥维耶多</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>国际米兰</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>1-3</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>负-负</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>大2.5</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>防1-2</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
+          <t>赫塔费</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>2.79</v>
       </c>
       <c r="M130" t="n">
-        <v>2</v>
-      </c>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>+8%</t>
-        </is>
-      </c>
-      <c r="W130" t="n">
-        <v>0</v>
-      </c>
-      <c r="X130" t="n">
-        <v>0</v>
+        <v>2.7</v>
+      </c>
+      <c r="N130" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>英超</t>
+          <t>德甲</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>周六023</t>
+          <t>周日023</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>曼城</t>
+          <t>美因茨</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>布伦特</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>4-1</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>大2.5</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>防3-1</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>9/10</t>
-        </is>
+          <t>柏林联合</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>1.58</v>
       </c>
       <c r="M131" t="n">
-        <v>2</v>
-      </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>+22%</t>
-        </is>
-      </c>
-      <c r="W131" t="n">
-        <v>0</v>
-      </c>
-      <c r="X131" t="n">
-        <v>0</v>
+        <v>3.8</v>
+      </c>
+      <c r="N131" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>德甲</t>
+          <t>沙职</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>周六024</t>
+          <t>周日024</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>沃夫斯堡</t>
+          <t>吉达联合</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>拜仁</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>1-4</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>负-负</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>大2.5</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>防1-3</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
+          <t>达马克</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>1.3</v>
       </c>
       <c r="M132" t="n">
-        <v>2</v>
-      </c>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>+19%</t>
-        </is>
-      </c>
-      <c r="W132" t="n">
-        <v>0</v>
-      </c>
-      <c r="X132" t="n">
-        <v>0</v>
+        <v>4.6</v>
+      </c>
+      <c r="N132" t="n">
+        <v>7</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>周六025</t>
+          <t>周日025</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>马竞</t>
+          <t>AC米兰</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>塞尔塔</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>大2.5</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>防4-1</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
+          <t>亚特兰大</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>1.9</v>
       </c>
       <c r="M133" t="n">
-        <v>2</v>
-      </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>+8%</t>
-        </is>
-      </c>
-      <c r="W133" t="n">
-        <v>0</v>
-      </c>
-      <c r="X133" t="n">
-        <v>0</v>
+        <v>3.28</v>
+      </c>
+      <c r="N133" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>02:45</t>
+        </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>美职</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>周六026</t>
+          <t>周日026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>多伦多</t>
+          <t>巴萨</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>迈国际</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>平-负</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>小2.5</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>防1-1</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
+          <t>皇马</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>1.51</v>
       </c>
       <c r="M134" t="n">
-        <v>2</v>
-      </c>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>+15%</t>
-        </is>
-      </c>
-      <c r="W134" t="n">
-        <v>0</v>
-      </c>
-      <c r="X134" t="n">
-        <v>0</v>
+        <v>4.65</v>
+      </c>
+      <c r="N134" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>沙职</t>
+          <t>法甲</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>周六027</t>
+          <t>周日027</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>迈季宽广</t>
+          <t>欧塞尔</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>胡巴卡德</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>负-负</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>小2.5</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>防0-2</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>9/10</t>
-        </is>
+          <t>尼斯</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>2.22</v>
       </c>
       <c r="M135" t="n">
-        <v>2</v>
-      </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>+24%</t>
-        </is>
-      </c>
-      <c r="W135" t="n">
-        <v>0</v>
-      </c>
-      <c r="X135" t="n">
-        <v>0</v>
+        <v>3.2</v>
+      </c>
+      <c r="N135" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>法乙</t>
+          <t>法甲</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>周六028</t>
+          <t>周日028</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>阿纳西</t>
+          <t>巴黎圣曼</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>罗德兹</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>平-胜</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>小2.5</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>防1-1</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
-      </c>
-      <c r="M136" t="n">
-        <v>2</v>
-      </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>+5%</t>
-        </is>
-      </c>
-      <c r="W136" t="n">
-        <v>0</v>
-      </c>
-      <c r="X136" t="n">
-        <v>0</v>
+          <t>布雷斯特</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>法甲</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>周六029</t>
+          <t>周日029</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>莱切</t>
+          <t>摩纳哥</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>尤文图斯</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>负-负</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>大2.5</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>防2-2</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>4/10</t>
-        </is>
+          <t>里尔</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>2.14</v>
       </c>
       <c r="M137" t="n">
-        <v>2</v>
-      </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>+15%</t>
-        </is>
-      </c>
-      <c r="W137" t="n">
-        <v>0</v>
-      </c>
-      <c r="X137" t="n">
-        <v>0</v>
+        <v>3.6</v>
+      </c>
+      <c r="N137" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>14场</t>
+          <t>竞彩</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>美职</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>周六030</t>
+          <t>周日030</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>皇家社会</t>
+          <t>纽约城</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>贝蒂斯</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>不投</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>大2.5</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>放弃</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>2/10</t>
-        </is>
+          <t>哥伦布</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>2.23</v>
       </c>
       <c r="M138" t="n">
-        <v>2</v>
-      </c>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>-10%</t>
-        </is>
-      </c>
-      <c r="W138" t="n">
-        <v>0</v>
-      </c>
-      <c r="X138" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>威廉二世</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>瓦尔韦克</t>
-        </is>
-      </c>
-      <c r="O139" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>塞维利亚</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>西班牙人</t>
-        </is>
-      </c>
-      <c r="O140" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>富勒姆</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>伯恩茅斯</t>
-        </is>
-      </c>
-      <c r="O141" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>桑德兰</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>曼联</t>
-        </is>
-      </c>
-      <c r="O142" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>莱红牛</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>圣保利</t>
-        </is>
-      </c>
-      <c r="O143" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>斯图加特</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>勒沃库森</t>
-        </is>
-      </c>
-      <c r="O144" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>霍芬海姆</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>不来梅</t>
-        </is>
-      </c>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>奥格斯堡</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>门兴</t>
-        </is>
-      </c>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>哥德堡</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>哈马比</t>
-        </is>
-      </c>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>代格福什</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>米亚尔比</t>
-        </is>
-      </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>卡利亚里</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>乌迪内斯</t>
-        </is>
-      </c>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>国际图尔</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>雅罗</t>
-        </is>
-      </c>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>萨普斯堡</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>腓特烈</t>
-        </is>
-      </c>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>埃尔切</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>阿拉维斯</t>
-        </is>
-      </c>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>米堡</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>南安普敦</t>
-        </is>
-      </c>
-      <c r="O153" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>利物浦</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>切尔西</t>
-        </is>
-      </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>波鸿</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>汉诺威96</t>
-        </is>
-      </c>
-      <c r="O155" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>大田市民</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>浦项制铁</t>
-        </is>
-      </c>
-      <c r="O156" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>光州FC</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>江原FC</t>
-        </is>
-      </c>
-      <c r="O157" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>大阪樱花</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>长崎航海</t>
-        </is>
-      </c>
-      <c r="O158" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>奥克兰FC</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>阿德莱德</t>
-        </is>
-      </c>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>莱万特</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>奥萨苏纳</t>
-        </is>
-      </c>
-      <c r="O160" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>赫尔城</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>米尔沃尔</t>
-        </is>
-      </c>
-      <c r="O161" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>朗斯</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>南特</t>
-        </is>
-      </c>
-      <c r="O162" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>都灵</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>萨索洛</t>
-        </is>
-      </c>
-      <c r="O163" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>多特蒙德</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>法兰克福</t>
-        </is>
-      </c>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>库奥皮奥</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>塞伊奈</t>
-        </is>
-      </c>
-      <c r="O165" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>汉坎</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>瓦勒伦加</t>
-        </is>
-      </c>
-      <c r="O166" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>埃夫斯堡</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>布鲁马波</t>
-        </is>
-      </c>
-      <c r="O167" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>凯泽</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>比勒费</t>
-        </is>
-      </c>
-      <c r="O168" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>威廉二世</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>瓦尔韦克</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>荷兰乙级联赛</t>
-        </is>
-      </c>
-      <c r="O169" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>塞维利亚</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>西班牙人</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>西班牙甲级联赛</t>
-        </is>
-      </c>
-      <c r="O170" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>富勒姆</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>伯恩茅斯</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>英格兰超级联赛</t>
-        </is>
-      </c>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>桑德兰</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>曼联</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>英格兰超级联赛</t>
-        </is>
-      </c>
-      <c r="O172" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>莱红牛</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>圣保利</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>德国甲级联赛</t>
-        </is>
-      </c>
-      <c r="O173" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>斯图加特</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>勒沃库森</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>德国甲级联赛</t>
-        </is>
-      </c>
-      <c r="O174" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>霍芬海姆</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>不来梅</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>德国甲级联赛</t>
-        </is>
-      </c>
-      <c r="O175" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>奥格斯堡</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>门兴</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>德国甲级联赛</t>
-        </is>
-      </c>
-      <c r="O176" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>哥德堡</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>哈马比</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>瑞典超级联赛</t>
-        </is>
-      </c>
-      <c r="O177" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>代格福什</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>米亚尔比</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>瑞典超级联赛</t>
-        </is>
-      </c>
-      <c r="O178" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>卡利亚里</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>乌迪内斯</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>意大利甲级联赛</t>
-        </is>
-      </c>
-      <c r="O179" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>国际图尔</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>雅罗</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>芬兰超级联赛</t>
-        </is>
-      </c>
-      <c r="O180" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>萨普斯堡</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>腓特烈</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>挪威超级联赛</t>
-        </is>
-      </c>
-      <c r="O181" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>埃尔切</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>阿拉维斯</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>西班牙甲级联赛</t>
-        </is>
-      </c>
-      <c r="O182" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>米堡</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>南安普敦</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>英格兰冠军联赛</t>
-        </is>
-      </c>
-      <c r="O183" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>利物浦</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>切尔西</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>英格兰超级联赛</t>
-        </is>
-      </c>
-      <c r="O184" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>波鸿</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>汉诺威96</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>德国乙级联赛</t>
-        </is>
-      </c>
-      <c r="O185" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>大田市民</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>浦项制铁</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>韩国职业联赛</t>
-        </is>
-      </c>
-      <c r="O186" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>光州FC</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>江原FC</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>韩国职业联赛</t>
-        </is>
-      </c>
-      <c r="O187" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>大阪樱花</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>长崎航海</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>日本职业联赛</t>
-        </is>
-      </c>
-      <c r="O188" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>奥克兰FC</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>阿德莱德</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>澳大利亚超级联赛</t>
-        </is>
-      </c>
-      <c r="O189" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>莱万特</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>奥萨苏纳</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>西班牙甲级联赛</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>平-平</t>
-        </is>
-      </c>
-      <c r="H190" t="n">
-        <v>3</v>
-      </c>
-      <c r="O190" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-      <c r="T190" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>赫尔城</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>米尔沃尔</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>英格兰冠军联赛</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>平-负</t>
-        </is>
-      </c>
-      <c r="H191" t="n">
-        <v>3</v>
-      </c>
-      <c r="O191" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-      <c r="T191" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>朗斯</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>南特</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>法国甲级联赛</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="H192" t="n">
-        <v>4</v>
-      </c>
-      <c r="O192" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-      <c r="T192" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>都灵</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>萨索洛</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>意大利甲级联赛</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>平-平</t>
-        </is>
-      </c>
-      <c r="H193" t="n">
-        <v>3</v>
-      </c>
-      <c r="O193" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-      <c r="T193" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>多特蒙德</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>法兰克福</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>德国甲级联赛</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="H194" t="n">
-        <v>5</v>
-      </c>
-      <c r="O194" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-      <c r="T194" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>库奥皮奥</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>塞伊奈</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>芬兰超级联赛</t>
-        </is>
-      </c>
-      <c r="O195" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>汉坎</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>瓦勒伦加</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>挪威超级联赛</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>平-平</t>
-        </is>
-      </c>
-      <c r="H196" t="n">
-        <v>3</v>
-      </c>
-      <c r="O196" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-      <c r="T196" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>埃夫斯堡</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>布鲁马波</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>瑞典超级联赛</t>
-        </is>
-      </c>
-      <c r="O197" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>凯泽</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>比勒费</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>德国乙级联赛</t>
-        </is>
-      </c>
-      <c r="O198" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>帕德博恩</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>卡斯鲁厄</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>德国乙级联赛</t>
-        </is>
-      </c>
-      <c r="O199" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>威廉二世</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>瓦尔韦克</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>荷兰乙级联赛</t>
-        </is>
-      </c>
-      <c r="O200" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>塞维利亚</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>西班牙人</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>西班牙甲级联赛</t>
-        </is>
-      </c>
-      <c r="O201" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>富勒姆</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>伯恩茅斯</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>英格兰超级联赛</t>
-        </is>
-      </c>
-      <c r="O202" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>桑德兰</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>曼联</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>英格兰超级联赛</t>
-        </is>
-      </c>
-      <c r="O203" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>莱红牛</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>圣保利</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>德国甲级联赛</t>
-        </is>
-      </c>
-      <c r="O204" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>斯图加特</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>勒沃库森</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>德国甲级联赛</t>
-        </is>
-      </c>
-      <c r="O205" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>霍芬海姆</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>不来梅</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>德国甲级联赛</t>
-        </is>
-      </c>
-      <c r="O206" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>奥格斯堡</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>门兴</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>德国甲级联赛</t>
-        </is>
-      </c>
-      <c r="O207" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>哥德堡</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>哈马比</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>瑞典超级联赛</t>
-        </is>
-      </c>
-      <c r="O208" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>代格福什</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>米亚尔比</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>瑞典超级联赛</t>
-        </is>
-      </c>
-      <c r="O209" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>卡利亚里</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>乌迪内斯</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>意大利甲级联赛</t>
-        </is>
-      </c>
-      <c r="O210" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>国际图尔</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>雅罗</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>芬兰超级联赛</t>
-        </is>
-      </c>
-      <c r="O211" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>萨普斯堡</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>腓特烈</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>挪威超级联赛</t>
-        </is>
-      </c>
-      <c r="O212" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>埃尔切</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>阿拉维斯</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>西班牙甲级联赛</t>
-        </is>
-      </c>
-      <c r="O213" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>米堡</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>南安普敦</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>英格兰冠军联赛</t>
-        </is>
-      </c>
-      <c r="O214" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>利物浦</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>切尔西</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>英格兰超级联赛</t>
-        </is>
-      </c>
-      <c r="O215" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>波鸿</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>汉诺威96</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>德国乙级联赛</t>
-        </is>
-      </c>
-      <c r="O216" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>大田市民</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>浦项制铁</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>韩国职业联赛</t>
-        </is>
-      </c>
-      <c r="O217" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>光州FC</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>江原FC</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>韩国职业联赛</t>
-        </is>
-      </c>
-      <c r="O218" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>大阪樱花</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>长崎航海</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>日本职业联赛</t>
-        </is>
-      </c>
-      <c r="O219" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>奥克兰FC</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>阿德莱德</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>澳大利亚超级联赛</t>
-        </is>
-      </c>
-      <c r="O220" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>莱万特</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>奥萨苏纳</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>西班牙甲级联赛</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>平-平</t>
-        </is>
-      </c>
-      <c r="H221" t="n">
-        <v>3</v>
-      </c>
-      <c r="O221" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-      <c r="T221" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>赫尔城</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>米尔沃尔</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>英格兰冠军联赛</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>平-负</t>
-        </is>
-      </c>
-      <c r="H222" t="n">
-        <v>3</v>
-      </c>
-      <c r="O222" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-      <c r="T222" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>朗斯</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>南特</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>法国甲级联赛</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="H223" t="n">
-        <v>4</v>
-      </c>
-      <c r="O223" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-      <c r="T223" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>都灵</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>萨索洛</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>意大利甲级联赛</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>平-平</t>
-        </is>
-      </c>
-      <c r="H224" t="n">
-        <v>3</v>
-      </c>
-      <c r="O224" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-      <c r="T224" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>多特蒙德</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>法兰克福</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>德国甲级联赛</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="H225" t="n">
-        <v>5</v>
-      </c>
-      <c r="O225" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-      <c r="T225" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>库奥皮奥</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>塞伊奈</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>芬兰超级联赛</t>
-        </is>
-      </c>
-      <c r="O226" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>汉坎</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>瓦勒伦加</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>挪威超级联赛</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>平-平</t>
-        </is>
-      </c>
-      <c r="H227" t="n">
-        <v>3</v>
-      </c>
-      <c r="O227" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-      <c r="T227" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>埃夫斯堡</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>布鲁马波</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>瑞典超级联赛</t>
-        </is>
-      </c>
-      <c r="O228" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>凯泽</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>比勒费</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>德国乙级联赛</t>
-        </is>
-      </c>
-      <c r="O229" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>帕德博恩</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>卡斯鲁厄</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>德国乙级联赛</t>
-        </is>
-      </c>
-      <c r="O230" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>威廉二世</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>瓦尔韦克</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>荷兰乙级联赛</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr"/>
-      <c r="H231" t="inlineStr"/>
-      <c r="O231" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>塞维利亚</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>西班牙人</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>西班牙甲级联赛</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr"/>
-      <c r="H232" t="inlineStr"/>
-      <c r="O232" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>富勒姆</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>伯恩茅斯</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>英格兰超级联赛</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr"/>
-      <c r="H233" t="inlineStr"/>
-      <c r="O233" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>桑德兰</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>曼联</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>英格兰超级联赛</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr"/>
-      <c r="H234" t="inlineStr"/>
-      <c r="O234" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>莱红牛</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>圣保利</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>德国甲级联赛</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr"/>
-      <c r="H235" t="inlineStr"/>
-      <c r="O235" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>斯图加特</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>勒沃库森</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>德国甲级联赛</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
-      <c r="O236" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>霍芬海姆</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>不来梅</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>德国甲级联赛</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr"/>
-      <c r="H237" t="inlineStr"/>
-      <c r="O237" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>奥格斯堡</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>门兴</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>德国甲级联赛</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr"/>
-      <c r="H238" t="inlineStr"/>
-      <c r="O238" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>哥德堡</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>哈马比</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>瑞典超级联赛</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr"/>
-      <c r="H239" t="inlineStr"/>
-      <c r="O239" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>代格福什</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>米亚尔比</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>瑞典超级联赛</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr"/>
-      <c r="H240" t="inlineStr"/>
-      <c r="O240" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>卡利亚里</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>乌迪内斯</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>意大利甲级联赛</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr"/>
-      <c r="H241" t="inlineStr"/>
-      <c r="O241" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>国际图尔</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>雅罗</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>芬兰超级联赛</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr"/>
-      <c r="O242" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>萨普斯堡</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>腓特烈</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>挪威超级联赛</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr"/>
-      <c r="H243" t="inlineStr"/>
-      <c r="O243" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>埃尔切</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>阿拉维斯</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>西班牙甲级联赛</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr"/>
-      <c r="H244" t="inlineStr"/>
-      <c r="O244" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>米堡</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>南安普敦</t>
-        </is>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>英格兰冠军联赛</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr"/>
-      <c r="H245" t="inlineStr"/>
-      <c r="O245" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>利物浦</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>切尔西</t>
-        </is>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>英格兰超级联赛</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr"/>
-      <c r="H246" t="inlineStr"/>
-      <c r="O246" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>波鸿</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>汉诺威96</t>
-        </is>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>德国乙级联赛</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr"/>
-      <c r="H247" t="inlineStr"/>
-      <c r="O247" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>大田市民</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>浦项制铁</t>
-        </is>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>韩国职业联赛</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr"/>
-      <c r="H248" t="inlineStr"/>
-      <c r="O248" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>光州FC</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>江原FC</t>
-        </is>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>韩国职业联赛</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr"/>
-      <c r="H249" t="inlineStr"/>
-      <c r="O249" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>大阪樱花</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>长崎航海</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>日本职业联赛</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr"/>
-      <c r="H250" t="inlineStr"/>
-      <c r="O250" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>奥克兰FC</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>阿德莱德</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>澳大利亚超级联赛</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr"/>
-      <c r="H251" t="inlineStr"/>
-      <c r="O251" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>莱万特</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>奥萨苏纳</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>西班牙甲级联赛</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>平-平</t>
-        </is>
-      </c>
-      <c r="H252" t="n">
-        <v>3</v>
-      </c>
-      <c r="O252" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-      <c r="T252" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>赫尔城</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>米尔沃尔</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>英格兰冠军联赛</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>平-负</t>
-        </is>
-      </c>
-      <c r="H253" t="n">
-        <v>3</v>
-      </c>
-      <c r="O253" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-      <c r="T253" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>朗斯</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>南特</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>法国甲级联赛</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="H254" t="n">
-        <v>4</v>
-      </c>
-      <c r="O254" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-      <c r="T254" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>都灵</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>萨索洛</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>意大利甲级联赛</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>平-平</t>
-        </is>
-      </c>
-      <c r="H255" t="n">
-        <v>3</v>
-      </c>
-      <c r="O255" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-      <c r="T255" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>多特蒙德</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>法兰克福</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>德国甲级联赛</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>胜-胜</t>
-        </is>
-      </c>
-      <c r="H256" t="n">
-        <v>5</v>
-      </c>
-      <c r="O256" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-      <c r="T256" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>库奥皮奥</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>塞伊奈</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>芬兰超级联赛</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr"/>
-      <c r="O257" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>汉坎</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>瓦勒伦加</t>
-        </is>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>挪威超级联赛</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>平-平</t>
-        </is>
-      </c>
-      <c r="H258" t="n">
-        <v>3</v>
-      </c>
-      <c r="O258" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-      <c r="T258" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>埃夫斯堡</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>布鲁马波</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>瑞典超级联赛</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr"/>
-      <c r="H259" t="inlineStr"/>
-      <c r="O259" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>凯泽</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>比勒费</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>德国乙级联赛</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr"/>
-      <c r="H260" t="inlineStr"/>
-      <c r="O260" t="inlineStr">
-        <is>
-          <t>待结算</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>帕德博恩</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>卡斯鲁厄</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>德国乙级联赛</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr"/>
-      <c r="H261" t="inlineStr"/>
-      <c r="O261" t="inlineStr">
-        <is>
-          <t>待结算</t>
+        <v>3.4</v>
+      </c>
+      <c r="N138" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>04:30</t>
         </is>
       </c>
     </row>
@@ -15161,7 +11652,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>

--- a/Aii竞彩数据总表.xlsx
+++ b/Aii竞彩数据总表.xlsx
@@ -669,8 +669,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU138"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:AU109"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
@@ -8324,50 +8324,38 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>澳超</t>
+          <t>威廉二世</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>周六001</t>
+          <t>瓦尔韦克</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>奥克兰FC</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>阿德莱德</t>
-        </is>
-      </c>
-      <c r="L79" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="M79" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N79" t="n">
-        <v>2.98</v>
-      </c>
+          <t>荷兰乙级联赛</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="O79" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="Y79" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -8384,50 +8372,38 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>日职</t>
+          <t>塞维利亚</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>周六002</t>
+          <t>西班牙人</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>大阪樱花</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>长崎航海</t>
-        </is>
-      </c>
-      <c r="L80" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="M80" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N80" t="n">
-        <v>3.8</v>
-      </c>
+          <t>西班牙甲级联赛</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="Y80" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA80" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -8444,50 +8420,38 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>韩职</t>
+          <t>富勒姆</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>周六003</t>
+          <t>伯恩茅斯</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>光州FC</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>江原FC</t>
-        </is>
-      </c>
-      <c r="L81" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="M81" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="N81" t="n">
-        <v>1.35</v>
-      </c>
+          <t>英格兰超级联赛</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="Y81" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AA81" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -8504,50 +8468,38 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>韩职</t>
+          <t>桑德兰</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>周六004</t>
+          <t>曼彻斯特联</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>大田市民</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>浦项制铁</t>
-        </is>
-      </c>
-      <c r="L82" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="M82" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="N82" t="n">
-        <v>3.45</v>
-      </c>
+          <t>英格兰超级联赛</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="Y82" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA82" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -8564,50 +8516,38 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>德乙</t>
+          <t>莱红牛</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>周六005</t>
+          <t>圣保利</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>波鸿</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>汉诺威96</t>
-        </is>
-      </c>
-      <c r="L83" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="M83" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N83" t="n">
-        <v>1.84</v>
-      </c>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="Y83" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z83" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AA83" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -8624,50 +8564,38 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>英超</t>
+          <t>斯图加特</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>周六006</t>
+          <t>勒沃库森</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>利物浦</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>切尔西</t>
-        </is>
-      </c>
-      <c r="L84" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M84" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N84" t="n">
-        <v>3.4</v>
-      </c>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="Y84" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Z84" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA84" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -8684,50 +8612,38 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>英冠</t>
+          <t>霍芬海姆</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>周六007</t>
+          <t>不来梅</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>米堡</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>南安普敦</t>
-        </is>
-      </c>
-      <c r="L85" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="M85" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N85" t="n">
-        <v>3.12</v>
-      </c>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="Y85" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA85" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -8744,50 +8660,38 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>奥格斯堡</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>周六008</t>
+          <t>门兴</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>埃尔切</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>阿拉维斯</t>
-        </is>
-      </c>
-      <c r="L86" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="M86" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N86" t="n">
-        <v>2.9</v>
-      </c>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="Y86" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="Z86" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AA86" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>20:00</t>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -8804,50 +8708,38 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>挪超</t>
+          <t>哥德堡</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>周六009</t>
+          <t>哈马比</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>萨普斯堡</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>腓特烈</t>
-        </is>
-      </c>
-      <c r="L87" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="M87" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N87" t="n">
-        <v>3.24</v>
-      </c>
+          <t>瑞典超级联赛</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="Y87" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="Z87" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA87" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>20:00</t>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -8864,50 +8756,38 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>芬超</t>
+          <t>代格福什</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>周六010</t>
+          <t>米亚尔比</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>国际图尔</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>雅罗</t>
-        </is>
-      </c>
-      <c r="L88" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M88" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N88" t="n">
-        <v>6.2</v>
-      </c>
+          <t>瑞典超级联赛</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="Y88" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z88" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA88" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>20:00</t>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -8924,50 +8804,38 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>卡利亚里</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>周六011</t>
+          <t>乌迪内斯</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>卡利亚里</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>乌迪内斯</t>
-        </is>
-      </c>
-      <c r="L89" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="M89" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N89" t="n">
-        <v>2.8</v>
-      </c>
+          <t>意大利甲级联赛</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="Y89" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Z89" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AA89" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>21:00</t>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -8984,50 +8852,38 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>瑞超</t>
+          <t>国际图尔</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>周六012</t>
+          <t>雅罗</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>代格福什</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>米亚尔比</t>
-        </is>
-      </c>
-      <c r="L90" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="M90" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N90" t="n">
-        <v>1.92</v>
-      </c>
+          <t>芬兰超级联赛</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="Y90" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z90" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA90" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>21:00</t>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -9044,50 +8900,38 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>瑞超</t>
+          <t>萨普斯堡</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>周六013</t>
+          <t>腓特烈</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>哥德堡</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>哈马比</t>
-        </is>
-      </c>
-      <c r="L91" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="M91" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N91" t="n">
-        <v>1.58</v>
-      </c>
+          <t>挪威超级联赛</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="Y91" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z91" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA91" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>21:00</t>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -9104,50 +8948,38 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>德甲</t>
+          <t>埃尔切</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>周六014</t>
+          <t>阿拉维斯</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>奥格斯堡</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>门兴</t>
-        </is>
-      </c>
-      <c r="L92" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="M92" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N92" t="n">
-        <v>3.15</v>
-      </c>
+          <t>西班牙甲级联赛</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="Y92" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="Z92" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA92" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -9164,50 +8996,38 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>德甲</t>
+          <t>米堡</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>周六015</t>
+          <t>南安普敦</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>霍芬海姆</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>不来梅</t>
-        </is>
-      </c>
-      <c r="L93" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M93" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="N93" t="n">
-        <v>5.6</v>
-      </c>
+          <t>英格兰冠军联赛</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="Y93" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Z93" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA93" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -9224,50 +9044,38 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>德甲</t>
+          <t>利物浦</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>周六016</t>
+          <t>切尔西</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>斯图加特</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>勒沃库森</t>
-        </is>
-      </c>
-      <c r="L94" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="M94" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N94" t="n">
-        <v>2.55</v>
-      </c>
+          <t>英格兰超级联赛</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="Y94" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="Z94" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA94" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -9284,50 +9092,38 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>德甲</t>
+          <t>波鸿</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>周六017</t>
+          <t>汉诺威96</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>莱红牛</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>圣保利</t>
-        </is>
-      </c>
-      <c r="L95" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M95" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N95" t="n">
-        <v>8.75</v>
-      </c>
+          <t>德国乙级联赛</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="Y95" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Z95" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA95" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -9344,50 +9140,38 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>英超</t>
+          <t>大田市民</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>周六018</t>
+          <t>浦项制铁</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>桑德兰</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>曼联</t>
-        </is>
-      </c>
-      <c r="L96" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="M96" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N96" t="n">
-        <v>1.74</v>
-      </c>
+          <t>韩国职业联赛</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="Y96" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z96" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA96" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>22:00</t>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -9404,50 +9188,38 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>英超</t>
+          <t>光州FC</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>周六019</t>
+          <t>江原FC</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>富勒姆</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>伯恩茅斯</t>
-        </is>
-      </c>
-      <c r="L97" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="M97" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N97" t="n">
-        <v>2.22</v>
-      </c>
+          <t>韩国职业联赛</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="Y97" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z97" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA97" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>22:00</t>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -9464,50 +9236,38 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>大阪樱花</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>周六020</t>
+          <t>长崎航海</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>塞维利亚</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>西班牙人</t>
-        </is>
-      </c>
-      <c r="L98" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M98" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N98" t="n">
-        <v>3.48</v>
-      </c>
+          <t>日本职业联赛</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="O98" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="Y98" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="Z98" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA98" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>22:15</t>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -9524,50 +9284,38 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>荷乙</t>
+          <t>奥克兰FC</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>周六021</t>
+          <t>阿德莱德</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>威廉二世</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>瓦尔韦克</t>
-        </is>
-      </c>
-      <c r="L99" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M99" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N99" t="n">
-        <v>3.15</v>
-      </c>
+          <t>澳大利亚超级联赛</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="Y99" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Z99" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA99" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>22:30</t>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -9584,50 +9332,38 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>莱万特</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>周六022</t>
+          <t>奥萨苏纳</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>拉齐奥</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>国际米兰</t>
-        </is>
-      </c>
-      <c r="L100" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M100" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N100" t="n">
-        <v>1.66</v>
-      </c>
+          <t>西班牙甲级联赛</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="Y100" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z100" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA100" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -9644,50 +9380,38 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>英超</t>
+          <t>赫尔城</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>周六023</t>
+          <t>米尔沃尔</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>曼城</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>布伦特</t>
-        </is>
-      </c>
-      <c r="L101" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M101" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="N101" t="n">
-        <v>7.1</v>
-      </c>
+          <t>英格兰冠军联赛</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="Y101" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z101" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA101" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>00:30</t>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -9704,50 +9428,38 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>德甲</t>
+          <t>朗斯</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>周六024</t>
+          <t>南特</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>沃夫斯堡</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>拜仁</t>
-        </is>
-      </c>
-      <c r="L102" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="M102" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N102" t="n">
-        <v>1.47</v>
-      </c>
+          <t>法国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="Y102" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Z102" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA102" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>00:30</t>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -9764,50 +9476,38 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>都灵</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>周六025</t>
+          <t>萨索洛</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>马竞</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>塞尔塔</t>
-        </is>
-      </c>
-      <c r="L103" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="M103" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N103" t="n">
-        <v>3.1</v>
-      </c>
+          <t>意大利甲级联赛</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="Y103" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Z103" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA103" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>00:30</t>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -9824,50 +9524,38 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>美职</t>
+          <t>多特蒙德</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>周六026</t>
+          <t>法兰克福</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>多伦多</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>迈国际</t>
-        </is>
-      </c>
-      <c r="L104" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="M104" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="N104" t="n">
-        <v>1.62</v>
-      </c>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="O104" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="Y104" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Z104" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA104" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>01:00</t>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -9884,50 +9572,38 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>沙职</t>
+          <t>库奥皮奥</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>周六027</t>
+          <t>塞伊奈约基</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>迈季宽广</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>胡巴卡德</t>
-        </is>
-      </c>
-      <c r="L105" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="M105" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="N105" t="n">
-        <v>1.35</v>
-      </c>
+          <t>芬兰超级联赛</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="Y105" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="Z105" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA105" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>02:00</t>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -9944,50 +9620,38 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>法乙</t>
+          <t>汉坎</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>周六028</t>
+          <t>瓦勒伦加</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>阿纳西</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>罗德兹</t>
-        </is>
-      </c>
-      <c r="L106" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="M106" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N106" t="n">
-        <v>2.8</v>
-      </c>
+          <t>挪威超级联赛</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="Y106" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Z106" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA106" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>02:00</t>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -10004,50 +9668,38 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>埃夫斯堡</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>周六029</t>
+          <t>布鲁马波卡纳</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>莱切</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>尤文图斯</t>
-        </is>
-      </c>
-      <c r="L107" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="M107" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="N107" t="n">
-        <v>1.32</v>
-      </c>
+          <t>瑞典超级联赛</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="Y107" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Z107" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA107" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>02:45</t>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
@@ -10064,57 +9716,45 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>凯泽斯劳滕</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>周六030</t>
+          <t>比勒费尔德</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>皇家社会</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>贝蒂斯</t>
-        </is>
-      </c>
-      <c r="L108" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="M108" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N108" t="n">
-        <v>2.41</v>
-      </c>
+          <t>德国乙级联赛</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="Y108" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z108" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA108" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>03:00</t>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10124,1520 +9764,47 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>韩职</t>
+          <t>帕德博恩</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>周日001</t>
+          <t>卡斯鲁厄</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>蔚山现代</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>富川FC</t>
-        </is>
-      </c>
-      <c r="L109" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M109" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N109" t="n">
-        <v>5.15</v>
-      </c>
+          <t>德国乙级联赛</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>日职</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>周日002</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>大阪钢巴</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>广岛三箭</t>
-        </is>
-      </c>
-      <c r="L110" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="M110" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N110" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>日职</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>周日003</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>柏太阳神</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>川崎前锋</t>
-        </is>
-      </c>
-      <c r="L111" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="M111" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N111" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>日职</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>周日004</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>千叶市原</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>町田泽维</t>
-        </is>
-      </c>
-      <c r="L112" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M112" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N112" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>意甲</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>周日005</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>维罗纳</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>科莫</t>
-        </is>
-      </c>
-      <c r="L113" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="M113" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="N113" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="O113" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>德乙</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>周日006</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>杜塞多夫</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>埃沃斯堡</t>
-        </is>
-      </c>
-      <c r="L114" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="M114" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="N114" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>西甲</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>周日007</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>马洛卡</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>比利亚雷</t>
-        </is>
-      </c>
-      <c r="L115" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="M115" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N115" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>挪超</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>周日008</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>罗森博格</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>利勒斯特</t>
-        </is>
-      </c>
-      <c r="L116" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="M116" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N116" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>英超</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>周日009</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>伯恩利</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>维拉</t>
-        </is>
-      </c>
-      <c r="L117" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="M117" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N117" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>英超</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>周日010</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>水晶宫</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>埃弗顿</t>
-        </is>
-      </c>
-      <c r="L118" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="M118" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N118" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>英超</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>周日011</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>诺丁汉</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>纽卡斯尔</t>
-        </is>
-      </c>
-      <c r="L119" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="M119" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="N119" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>意甲</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>周日012</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>克雷莫纳</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>比萨</t>
-        </is>
-      </c>
-      <c r="L120" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M120" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N120" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>意甲</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>周日013</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>佛罗伦萨</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>热那亚</t>
-        </is>
-      </c>
-      <c r="L121" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="M121" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N121" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O121" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>德甲</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>周日014</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>汉堡</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>弗赖堡</t>
-        </is>
-      </c>
-      <c r="L122" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="M122" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N122" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>西甲</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>周日015</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>毕尔巴鄂</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>巴伦西亚</t>
-        </is>
-      </c>
-      <c r="L123" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M123" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N123" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="O123" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>22:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>荷甲</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>周日016</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>费耶诺德</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>阿尔克马</t>
-        </is>
-      </c>
-      <c r="L124" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="M124" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="N124" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>22:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>荷甲</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>周日017</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>阿贾克斯</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>乌德勒支</t>
-        </is>
-      </c>
-      <c r="L125" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M125" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="N125" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>22:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>荷甲</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>周日018</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>格罗宁根</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>奈梅亨</t>
-        </is>
-      </c>
-      <c r="L126" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="M126" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N126" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>22:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>英超</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>周日019</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>西汉姆联</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>阿森纳</t>
-        </is>
-      </c>
-      <c r="L127" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M127" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N127" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>德甲</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>周日020</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>科隆</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>海登海姆</t>
-        </is>
-      </c>
-      <c r="L128" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M128" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N128" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>意甲</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>周日021</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>帕尔马</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>罗马</t>
-        </is>
-      </c>
-      <c r="L129" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="M129" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N129" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>西甲</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>周日022</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>奥维耶多</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>赫塔费</t>
-        </is>
-      </c>
-      <c r="L130" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="M130" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N130" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O130" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>德甲</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>周日023</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>美因茨</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>柏林联合</t>
-        </is>
-      </c>
-      <c r="L131" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="M131" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N131" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="O131" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>沙职</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>周日024</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>吉达联合</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>达马克</t>
-        </is>
-      </c>
-      <c r="L132" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M132" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N132" t="n">
-        <v>7</v>
-      </c>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>02:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>意甲</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>周日025</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AC米兰</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>亚特兰大</t>
-        </is>
-      </c>
-      <c r="L133" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M133" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="N133" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O133" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>02:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>西甲</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>周日026</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>巴萨</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>皇马</t>
-        </is>
-      </c>
-      <c r="L134" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M134" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="N134" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="O134" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>法甲</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>周日027</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>欧塞尔</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>尼斯</t>
-        </is>
-      </c>
-      <c r="L135" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="M135" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N135" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="O135" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>法甲</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>周日028</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>巴黎圣曼</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>布雷斯特</t>
-        </is>
-      </c>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>法甲</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>周日029</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>摩纳哥</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>里尔</t>
-        </is>
-      </c>
-      <c r="L137" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="M137" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N137" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>竞彩</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>美职</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>周日030</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>纽约城</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>哥伦布</t>
-        </is>
-      </c>
-      <c r="L138" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="M138" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N138" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O138" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>04:30</t>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>复盘写入 v2 @ 05-10 16:41</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:V50"/>
   <mergeCells count="4">
+    <mergeCell ref="T1:V1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:N1"/>
-    <mergeCell ref="T1:V1"/>
     <mergeCell ref="O1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11652,7 +9819,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>

--- a/Aii竞彩数据总表.xlsx
+++ b/Aii竞彩数据总表.xlsx
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU109"/>
+  <dimension ref="A1:AU117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8314,7 +8314,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8324,45 +8324,49 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>威廉二世</t>
+          <t>英格兰超级联赛</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>瓦尔韦克</t>
+          <t>001</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>荷兰乙级联赛</t>
+          <t>曼城</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>谢菲联</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>不投</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>⏳</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>✅</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8372,17 +8376,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>塞维利亚</t>
+          <t>芬兰超级联赛</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>西班牙人</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>西班牙甲级联赛</t>
+          <t>坦佩雷山猫</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>AC奥卢</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -8390,10 +8399,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -8403,14 +8431,14 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8420,17 +8448,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>富勒姆</t>
+          <t>芬兰超级联赛</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>伯恩茅斯</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>英格兰超级联赛</t>
+          <t>TPS图尔库</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>赫尔辛基</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -8438,10 +8471,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>负-负</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
@@ -8451,14 +8503,14 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8468,17 +8520,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>桑德兰</t>
+          <t>南美解放者杯</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>曼彻斯特联</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>英格兰超级联赛</t>
+          <t>米拉索尔</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>基多体育大学</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -8486,10 +8543,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>让平+让负</t>
+        </is>
+      </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -8499,14 +8575,14 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8516,17 +8592,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>莱红牛</t>
+          <t>欧洲协会联赛</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>圣保利</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>德国甲级联赛</t>
+          <t>斯特拉斯堡</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>巴列卡诺</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -8534,10 +8615,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>让负</t>
+        </is>
+      </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -8547,14 +8647,14 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8564,17 +8664,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>斯图加特</t>
+          <t>欧罗巴联赛</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>勒沃库森</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>德国甲级联赛</t>
+          <t>维拉</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>诺丁汉森林</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -8582,10 +8687,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>让平+让负</t>
+        </is>
+      </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
@@ -8595,14 +8719,14 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8612,17 +8736,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>霍芬海姆</t>
+          <t>欧罗巴联赛</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>不来梅</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>德国甲级联赛</t>
+          <t>弗赖堡</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>布拉加</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -8630,10 +8759,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>让平+让负</t>
+        </is>
+      </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
@@ -8643,14 +8791,14 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8660,17 +8808,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>奥格斯堡</t>
+          <t>沙特职业联赛</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>门兴</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>德国甲级联赛</t>
+          <t>利雅得青年</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>利雅得胜利</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -8678,10 +8831,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>让平+让胜</t>
+        </is>
+      </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -8691,7 +8863,7 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -8708,17 +8880,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>哥德堡</t>
+          <t>荷兰乙级联赛</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>哈马比</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>瑞典超级联赛</t>
+          <t>威廉二世</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>瓦尔韦克</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -8726,10 +8903,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -8739,7 +8935,7 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -8756,17 +8952,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>代格福什</t>
+          <t>西班牙甲级联赛</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>米亚尔比</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>瑞典超级联赛</t>
+          <t>塞维利亚</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>西班牙人</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -8774,10 +8975,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -8787,7 +9007,7 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -8804,17 +9024,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>卡利亚里</t>
+          <t>英格兰超级联赛</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>乌迪内斯</t>
+          <t>6019</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>意大利甲级联赛</t>
+          <t>富勒姆</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>伯恩茅斯</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -8822,10 +9047,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
@@ -8835,7 +9079,7 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -8852,17 +9096,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>国际图尔</t>
+          <t>英格兰超级联赛</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>雅罗</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>芬兰超级联赛</t>
+          <t>桑德兰</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>曼彻斯特联</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -8870,10 +9119,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
@@ -8883,7 +9151,7 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -8900,17 +9168,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>萨普斯堡</t>
+          <t>德国甲级联赛</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>腓特烈</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>挪威超级联赛</t>
+          <t>莱红牛</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>圣保利</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -8918,7 +9191,26 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O91" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -8931,7 +9223,7 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -8948,17 +9240,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>埃尔切</t>
+          <t>德国甲级联赛</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>阿拉维斯</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>西班牙甲级联赛</t>
+          <t>斯图加特</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>勒沃库森</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -8966,10 +9263,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
@@ -8979,7 +9295,7 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -8996,17 +9312,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>米堡</t>
+          <t>德国甲级联赛</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>南安普敦</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>英格兰冠军联赛</t>
+          <t>霍芬海姆</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>不来梅</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -9014,10 +9335,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
@@ -9027,7 +9367,7 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -9044,17 +9384,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>利物浦</t>
+          <t>德国甲级联赛</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>切尔西</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>英格兰超级联赛</t>
+          <t>奥格斯堡</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>门兴</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -9062,10 +9407,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
@@ -9075,7 +9439,7 @@
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -9092,17 +9456,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>波鸿</t>
+          <t>瑞典超级联赛</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>汉诺威96</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>德国乙级联赛</t>
+          <t>哥德堡</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>哈马比</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -9110,10 +9479,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
@@ -9123,7 +9511,7 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -9140,17 +9528,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>大田市民</t>
+          <t>瑞典超级联赛</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>浦项制铁</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>韩国职业联赛</t>
+          <t>代格福什</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>米亚尔比</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -9158,10 +9551,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
@@ -9171,7 +9583,7 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -9188,17 +9600,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>光州FC</t>
+          <t>意大利甲级联赛</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>江原FC</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>韩国职业联赛</t>
+          <t>卡利亚里</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>乌迪内斯</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -9206,10 +9623,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
@@ -9219,7 +9655,7 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -9236,17 +9672,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>大阪樱花</t>
+          <t>芬兰超级联赛</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>长崎航海</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>日本职业联赛</t>
+          <t>国际图尔</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>雅罗</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -9254,10 +9695,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
@@ -9267,7 +9727,7 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -9284,17 +9744,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>奥克兰FC</t>
+          <t>挪威超级联赛</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>阿德莱德</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>澳大利亚超级联赛</t>
+          <t>萨普斯堡</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>腓特烈</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -9302,10 +9767,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
@@ -9315,7 +9799,7 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -9332,17 +9816,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>莱万特</t>
+          <t>西班牙甲级联赛</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>奥萨苏纳</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>西班牙甲级联赛</t>
+          <t>埃尔切</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>阿拉维斯</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -9350,10 +9839,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
@@ -9363,7 +9871,7 @@
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -9380,17 +9888,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>赫尔城</t>
+          <t>英格兰冠军联赛</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>米尔沃尔</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>英格兰冠军联赛</t>
+          <t>米堡</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>南安普敦</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -9398,7 +9911,26 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O101" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -9411,7 +9943,7 @@
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -9428,17 +9960,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>朗斯</t>
+          <t>英格兰超级联赛</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>南特</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>法国甲级联赛</t>
+          <t>利物浦</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>切尔西</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -9446,10 +9983,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
@@ -9459,7 +10015,7 @@
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -9476,17 +10032,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>都灵</t>
+          <t>德国乙级联赛</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>萨索洛</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>意大利甲级联赛</t>
+          <t>波鸿</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>汉诺威96</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -9494,10 +10055,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -9507,7 +10087,7 @@
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -9524,17 +10104,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>多特蒙德</t>
+          <t>韩国职业联赛</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>法兰克福</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>德国甲级联赛</t>
+          <t>大田市民</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>浦项制铁</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -9542,10 +10127,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -9555,7 +10159,7 @@
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -9572,17 +10176,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>库奥皮奥</t>
+          <t>韩国职业联赛</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>塞伊奈约基</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>芬兰超级联赛</t>
+          <t>光州FC</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>江原FC</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -9590,7 +10199,26 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O105" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -9603,7 +10231,7 @@
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -9620,17 +10248,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>汉坎</t>
+          <t>日本职业联赛</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>瓦勒伦加</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>挪威超级联赛</t>
+          <t>大阪樱花</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>长崎航海</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -9638,10 +10271,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
@@ -9651,7 +10303,7 @@
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -9668,17 +10320,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>埃夫斯堡</t>
+          <t>澳大利亚超级联赛</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>布鲁马波卡纳</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>瑞典超级联赛</t>
+          <t>奥克兰FC</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>阿德莱德</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -9686,10 +10343,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
@@ -9699,7 +10375,7 @@
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -9716,17 +10392,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>凯泽斯劳滕</t>
+          <t>西班牙甲级联赛</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>比勒费尔德</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>德国乙级联赛</t>
+          <t>莱万特</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>奥萨苏纳</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -9734,10 +10415,29 @@
           <t>不投</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
@@ -9747,7 +10447,7 @@
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -9764,47 +10464,647 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
+          <t>英格兰冠军联赛</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>5011</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>赫尔城</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>米尔沃尔</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 18:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>法国甲级联赛</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>5010</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>朗斯</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>南特</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>胜-胜</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 18:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>意大利甲级联赛</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>5009</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>都灵</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>萨索洛</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 18:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>5008</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>多特蒙德</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>法兰克福</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>胜-胜</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 18:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>芬兰超级联赛</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>5007</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>库奥皮奥</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>塞伊奈约基</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>胜-胜</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 18:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>挪威超级联赛</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>5006</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>汉坎</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>瓦勒伦加</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 18:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>瑞典超级联赛</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>埃夫斯堡</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>布鲁马波卡纳</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 18:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>德国乙级联赛</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>5004</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>凯泽斯劳滕</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>比勒费尔德</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 18:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>德国乙级联赛</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>5003</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
           <t>帕德博恩</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="F117" t="inlineStr">
         <is>
           <t>卡斯鲁厄</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>德国乙级联赛</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t>不投</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="O109" t="inlineStr">
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
         <is>
           <t>2-2</t>
         </is>
       </c>
-      <c r="T109" t="inlineStr">
+      <c r="T117" t="inlineStr">
         <is>
           <t>⏳</t>
         </is>
       </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>复盘写入 v2 @ 05-10 16:41</t>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:V50"/>
   <mergeCells count="4">
-    <mergeCell ref="T1:V1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:N1"/>
+    <mergeCell ref="T1:V1"/>
     <mergeCell ref="O1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Aii竞彩数据总表.xlsx
+++ b/Aii竞彩数据总表.xlsx
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU117"/>
+  <dimension ref="A1:AU130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11099,11 +11099,947 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>日本职业联赛</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>7004</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>千叶市原</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>町田泽维</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>平负</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>让平/让负</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 19:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>日本职业联赛</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>7003</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>柏太阳神</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>川崎前锋</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>让平/让负</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 19:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>日本职业联赛</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>7002</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>大阪钢巴</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>广岛三箭</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>平负</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>让平/让负</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 19:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>韩国职业联赛</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>7001</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>蔚山现代</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>富川FC</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>让平/让负</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 19:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>西班牙甲级联赛</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>6030</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>皇家社会</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>贝蒂斯</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 19:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>意大利甲级联赛</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>6029</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>莱切</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>尤文图斯</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 19:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>法国乙级联赛</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>6028</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>阿纳西</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>罗德兹</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 19:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>沙特职业联赛</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>6027</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>迈季宽广</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>胡巴卡德</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 19:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>美国职业大联盟</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>6026</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>多伦多</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>迈国际</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 19:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>西班牙甲级联赛</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>6025</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>马竞</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>塞尔塔</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 19:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>6024</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>沃夫斯堡</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>拜仁慕尼黑</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 19:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>英格兰超级联赛</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>6023</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>曼彻斯特城</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>布伦特</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 19:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>意大利甲级联赛</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>6022</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>拉齐奥</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>国际米兰</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>复盘 @ 05-10 19:06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:V50"/>
   <mergeCells count="4">
+    <mergeCell ref="G1:N1"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:N1"/>
     <mergeCell ref="T1:V1"/>
     <mergeCell ref="O1:S1"/>
   </mergeCells>

--- a/Aii竞彩数据总表.xlsx
+++ b/Aii竞彩数据总表.xlsx
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU130"/>
+  <dimension ref="A1:AU135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8366,7 +8366,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8376,69 +8376,94 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>芬兰超级联赛</t>
+          <t>日本职业联赛</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>坦佩雷山猫</t>
+          <t>千叶市原</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AC奥卢</t>
+          <t>町田泽维</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>不投</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
+          <t>平负</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>让平/让负</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
           <t>平-负</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>1-0</t>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>⏳</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
+          <t>部分正确</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>方向客胜命中; 大小球小2.5命中; 半全场平负实际平-负</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8448,47 +8473,52 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>芬兰超级联赛</t>
+          <t>日本职业联赛</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>TPS图尔库</t>
+          <t>柏太阳神</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>赫尔辛基</t>
+          <t>川崎前锋</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>不投</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>负-负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>让平/让负</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2/10</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -8496,21 +8526,41 @@
           <t>1-0</t>
         </is>
       </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>⏳</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
+          <t>部分正确</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>方向主胜命中; 大小球小2.5命中; 半全场胜胜实际平-胜</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8520,69 +8570,94 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>南美解放者杯</t>
+          <t>日本职业联赛</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>米拉索尔</t>
+          <t>大阪钢巴</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>基多体育大学</t>
+          <t>广岛三箭</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>不投</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>平负</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>让平+让负</t>
+          <t>让平/让负</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2/10</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>⏳</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
+          <t>部分正确</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>方向客胜命中; 大小球小2.5命中; 半全场平负实际平-负</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8592,69 +8667,94 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>欧洲协会联赛</t>
+          <t>韩国职业联赛</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>斯特拉斯堡</t>
+          <t>蔚山现代</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>巴列卡诺</t>
+          <t>富川FC</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>不投</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>让负</t>
+          <t>让平/让负</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2/10</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>⏳</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
+          <t>部分正确</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>方向主胜命中; 大小球小2.5命中; 半全场胜胜实际平-胜</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8664,22 +8764,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>欧罗巴联赛</t>
+          <t>西班牙甲级联赛</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>维拉</t>
+          <t>皇家社会</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>诺丁汉森林</t>
+          <t>贝蒂斯</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -8704,29 +8804,44 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>让平+让负</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>大2.5</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
           <t>⏳</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8736,22 +8851,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>欧罗巴联赛</t>
+          <t>意大利甲级联赛</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>弗赖堡</t>
+          <t>莱切</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>布拉加</t>
+          <t>尤文图斯</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -8776,29 +8891,44 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>让平+让负</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
           <t>⏳</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8808,22 +8938,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>沙特职业联赛</t>
+          <t>法国乙级联赛</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>利雅得青年</t>
+          <t>阿纳西</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>利雅得胜利</t>
+          <t>罗德兹</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -8848,29 +8978,44 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>让平+让胜</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>大2.5</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
           <t>⏳</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8880,22 +9025,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>荷兰乙级联赛</t>
+          <t>沙特职业联赛</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>威廉二世</t>
+          <t>迈季宽广</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>瓦尔韦克</t>
+          <t>胡巴卡德</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -8925,24 +9070,39 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>大2.5</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
           <t>⏳</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8952,22 +9112,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>西班牙甲级联赛</t>
+          <t>美国职业大联盟</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>塞维利亚</t>
+          <t>多伦多</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>西班牙人</t>
+          <t>迈国际</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -8997,24 +9157,39 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>大2.5</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
           <t>⏳</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9024,22 +9199,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>英格兰超级联赛</t>
+          <t>西班牙甲级联赛</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>富勒姆</t>
+          <t>马竞</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>伯恩茅斯</t>
+          <t>塞尔塔</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -9072,21 +9247,36 @@
           <t>0-1</t>
         </is>
       </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
       <c r="T89" t="inlineStr">
         <is>
           <t>⏳</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9096,22 +9286,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>英格兰超级联赛</t>
+          <t>德国甲级联赛</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>桑德兰</t>
+          <t>沃夫斯堡</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>曼彻斯特联</t>
+          <t>拜仁慕尼黑</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -9141,24 +9331,39 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
           <t>0-0</t>
         </is>
       </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
       <c r="T90" t="inlineStr">
         <is>
           <t>⏳</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9168,22 +9373,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>德国甲级联赛</t>
+          <t>英格兰超级联赛</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>莱红牛</t>
+          <t>曼彻斯特城</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>圣保利</t>
+          <t>布伦特</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -9213,24 +9418,39 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>大2.5</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
           <t>⏳</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9240,22 +9460,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>德国甲级联赛</t>
+          <t>意大利甲级联赛</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>斯图加特</t>
+          <t>拉齐奥</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>勒沃库森</t>
+          <t>国际米兰</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -9285,24 +9505,39 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>大2.5</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
           <t>⏳</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9312,22 +9547,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>德国甲级联赛</t>
+          <t>南美解放者杯</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>霍芬海姆</t>
+          <t>圣菲独立</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>不来梅</t>
+          <t>科林蒂安</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -9357,24 +9592,39 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
           <t>⏳</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9384,22 +9634,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>德国甲级联赛</t>
+          <t>南美解放者杯</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>奥格斯堡</t>
+          <t>里独立</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>门兴</t>
+          <t>弗鲁米嫩</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -9429,24 +9679,39 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
           <t>⏳</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9456,22 +9721,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>瑞典超级联赛</t>
+          <t>欧洲冠军联赛</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>哥德堡</t>
+          <t>拜仁慕尼黑</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>哈马比</t>
+          <t>巴黎圣曼</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -9501,24 +9766,39 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
           <t>0-1</t>
         </is>
       </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
       <c r="T95" t="inlineStr">
         <is>
           <t>⏳</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9528,22 +9808,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>瑞典超级联赛</t>
+          <t>沙特职业联赛</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>代格福什</t>
+          <t>吉达国民</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>米亚尔比</t>
+          <t>穆拜征服</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -9573,24 +9853,39 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>大2.5</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
           <t>⏳</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9600,22 +9895,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>意大利甲级联赛</t>
+          <t>荷兰乙级联赛</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>卡利亚里</t>
+          <t>阿尔梅勒</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>乌迪内斯</t>
+          <t>格拉夫</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -9645,24 +9940,39 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>大2.5</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
         <is>
           <t>⏳</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9677,17 +9987,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>国际图尔</t>
+          <t>坦佩雷山猫</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>雅罗</t>
+          <t>AC奥卢</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -9702,7 +10012,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>平-负</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -9717,7 +10027,27 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
@@ -9725,16 +10055,16 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>半全场平-负实际平-胜</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9744,22 +10074,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>挪威超级联赛</t>
+          <t>芬兰超级联赛</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>萨普斯堡</t>
+          <t>TPS图尔库</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>腓特烈</t>
+          <t>赫尔辛基</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -9774,7 +10104,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>负-负</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -9789,7 +10119,27 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
@@ -9797,16 +10147,16 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>半全场负-负实际平-胜</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9816,22 +10166,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>西班牙甲级联赛</t>
+          <t>南美解放者杯</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>埃尔切</t>
+          <t>米拉索尔</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>阿拉维斯</t>
+          <t>基多体育大学</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -9856,29 +10206,44 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>让平+让负</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
         <is>
           <t>⏳</t>
-        </is>
-      </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9888,22 +10253,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>英格兰冠军联赛</t>
+          <t>欧洲协会联赛</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>米堡</t>
+          <t>斯特拉斯堡</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>南安普敦</t>
+          <t>巴列卡诺</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -9928,29 +10293,44 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>让负</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
         <is>
           <t>⏳</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9960,22 +10340,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>英格兰超级联赛</t>
+          <t>欧罗巴联赛</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>利物浦</t>
+          <t>维拉</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>切尔西</t>
+          <t>诺丁汉森林</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -10000,29 +10380,44 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>让平+让负</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>大2.5</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
         <is>
           <t>⏳</t>
-        </is>
-      </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10032,22 +10427,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>德国乙级联赛</t>
+          <t>欧罗巴联赛</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>波鸿</t>
+          <t>弗赖堡</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>汉诺威96</t>
+          <t>布拉加</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -10072,29 +10467,44 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>让平+让负</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>大2.5</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
         <is>
           <t>⏳</t>
-        </is>
-      </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10104,22 +10514,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>韩国职业联赛</t>
+          <t>沙特职业联赛</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>大田市民</t>
+          <t>利雅得青年</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>浦项制铁</t>
+          <t>利雅得胜利</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -10144,22 +10554,37 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>让平+让胜</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>负-负</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>大2.5</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
           <t>⏳</t>
-        </is>
-      </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
         </is>
       </c>
     </row>
@@ -10176,22 +10601,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>韩国职业联赛</t>
+          <t>荷兰乙级联赛</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>光州FC</t>
+          <t>威廉二世</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>江原FC</t>
+          <t>瓦尔韦克</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -10219,21 +10644,41 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
           <t>0-0</t>
         </is>
       </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
       <c r="T105" t="inlineStr">
         <is>
           <t>⏳</t>
         </is>
       </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
-        </is>
-      </c>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10248,22 +10693,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>日本职业联赛</t>
+          <t>西班牙甲级联赛</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>大阪樱花</t>
+          <t>塞维利亚</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>长崎航海</t>
+          <t>西班牙人</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -10291,9 +10736,32 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>大2.5</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
@@ -10301,11 +10769,8 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="V106" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
-        </is>
-      </c>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -10320,22 +10785,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>澳大利亚超级联赛</t>
+          <t>英格兰超级联赛</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6019</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>奥克兰FC</t>
+          <t>富勒姆</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>阿德莱德</t>
+          <t>伯恩茅斯</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -10363,9 +10828,32 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
@@ -10373,11 +10861,8 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="V107" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
-        </is>
-      </c>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -10392,22 +10877,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>西班牙甲级联赛</t>
+          <t>英格兰超级联赛</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>莱万特</t>
+          <t>桑德兰</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>奥萨苏纳</t>
+          <t>曼彻斯特联</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -10422,22 +10907,45 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
           <t>平-平</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>3-2</t>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
@@ -10445,11 +10953,8 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
-        </is>
-      </c>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -10464,22 +10969,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>英格兰冠军联赛</t>
+          <t>德国甲级联赛</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>赫尔城</t>
+          <t>莱红牛</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>米尔沃尔</t>
+          <t>圣保利</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -10494,7 +10999,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>平-负</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -10507,9 +11012,32 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>大2.5</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
@@ -10517,11 +11045,8 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
-        </is>
-      </c>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10536,22 +11061,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>法国甲级联赛</t>
+          <t>德国甲级联赛</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>朗斯</t>
+          <t>斯图加特</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>南特</t>
+          <t>勒沃库森</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -10566,22 +11091,45 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
           <t>胜-胜</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>1-0</t>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>大2.5</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
@@ -10589,11 +11137,8 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
-        </is>
-      </c>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10608,22 +11153,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>意大利甲级联赛</t>
+          <t>德国甲级联赛</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>都灵</t>
+          <t>霍芬海姆</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>萨索洛</t>
+          <t>不来梅</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -10638,7 +11183,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>平-平</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -10651,9 +11196,32 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
@@ -10661,11 +11229,8 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="V111" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
-        </is>
-      </c>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10685,17 +11250,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>多特蒙德</t>
+          <t>奥格斯堡</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>法兰克福</t>
+          <t>门兴</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -10710,7 +11275,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>胜-胜</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -10723,9 +11288,32 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>大2.5</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
@@ -10733,11 +11321,8 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
-        </is>
-      </c>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -10752,22 +11337,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>芬兰超级联赛</t>
+          <t>瑞典超级联赛</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>库奥皮奥</t>
+          <t>哥德堡</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>塞伊奈约基</t>
+          <t>哈马比</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -10782,7 +11367,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>胜-胜</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -10795,21 +11380,41 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
           <t>0-0</t>
         </is>
       </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
       <c r="T113" t="inlineStr">
         <is>
           <t>⏳</t>
         </is>
       </c>
-      <c r="V113" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
-        </is>
-      </c>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10824,22 +11429,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>挪威超级联赛</t>
+          <t>瑞典超级联赛</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>汉坎</t>
+          <t>代格福什</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>瓦勒伦加</t>
+          <t>米亚尔比</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -10854,7 +11459,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>平-平</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -10867,9 +11472,32 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>大2.5</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
@@ -10877,11 +11505,8 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
-        </is>
-      </c>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10896,22 +11521,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>瑞典超级联赛</t>
+          <t>意大利甲级联赛</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>埃夫斯堡</t>
+          <t>卡利亚里</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>布鲁马波卡纳</t>
+          <t>乌迪内斯</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -10939,9 +11564,32 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
@@ -10949,11 +11597,8 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
-        </is>
-      </c>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10968,22 +11613,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>德国乙级联赛</t>
+          <t>芬兰超级联赛</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>凯泽斯劳滕</t>
+          <t>国际图尔</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>比勒费尔德</t>
+          <t>雅罗</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -10998,7 +11643,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>平-负</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -11011,21 +11656,41 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
           <t>2-0</t>
         </is>
       </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
       <c r="T116" t="inlineStr">
         <is>
           <t>⏳</t>
         </is>
       </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
-        </is>
-      </c>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -11040,22 +11705,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>德国乙级联赛</t>
+          <t>挪威超级联赛</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>帕德博恩</t>
+          <t>萨普斯堡</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>卡斯鲁厄</t>
+          <t>腓特烈</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -11083,9 +11748,32 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>大2.5</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -11093,16 +11781,13 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="V117" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 18:57</t>
-        </is>
-      </c>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11112,69 +11797,89 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>日本职业联赛</t>
+          <t>西班牙甲级联赛</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>千叶市原</t>
+          <t>埃尔切</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>町田泽维</t>
+          <t>阿拉维斯</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>不投</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
           <t>小2.5</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>让平/让负</t>
-        </is>
-      </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 19:06</t>
-        </is>
-      </c>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11184,69 +11889,89 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>日本职业联赛</t>
+          <t>英格兰冠军联赛</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>柏太阳神</t>
+          <t>米堡</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>川崎前锋</t>
+          <t>南安普敦</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>不投</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
           <t>小2.5</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>让平/让负</t>
-        </is>
-      </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 19:06</t>
-        </is>
-      </c>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11256,69 +11981,89 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>日本职业联赛</t>
+          <t>英格兰超级联赛</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>大阪钢巴</t>
+          <t>利物浦</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>广岛三箭</t>
+          <t>切尔西</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>不投</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
           <t>小2.5</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>让平/让负</t>
-        </is>
-      </c>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 19:06</t>
-        </is>
-      </c>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11328,69 +12073,89 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>韩国职业联赛</t>
+          <t>德国乙级联赛</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>蔚山现代</t>
+          <t>波鸿</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>富川FC</t>
+          <t>汉诺威96</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>不投</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
           <t>小2.5</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>让平/让负</t>
-        </is>
-      </c>
-      <c r="O121" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 19:06</t>
-        </is>
-      </c>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11400,22 +12165,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>西班牙甲级联赛</t>
+          <t>韩国职业联赛</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>皇家社会</t>
+          <t>大田市民</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>贝蒂斯</t>
+          <t>浦项制铁</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -11443,9 +12208,32 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
@@ -11453,16 +12241,13 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 19:06</t>
-        </is>
-      </c>
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11472,22 +12257,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>意大利甲级联赛</t>
+          <t>韩国职业联赛</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>莱切</t>
+          <t>光州FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>尤文图斯</t>
+          <t>江原FC</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -11515,9 +12300,32 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
@@ -11525,16 +12333,13 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 19:06</t>
-        </is>
-      </c>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11544,22 +12349,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>法国乙级联赛</t>
+          <t>日本职业联赛</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>阿纳西</t>
+          <t>大阪樱花</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>罗德兹</t>
+          <t>长崎航海</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -11587,9 +12392,32 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>大2.5</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
@@ -11597,16 +12425,13 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 19:06</t>
-        </is>
-      </c>
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11616,22 +12441,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>沙特职业联赛</t>
+          <t>澳大利亚超级联赛</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>迈季宽广</t>
+          <t>奥克兰FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>胡巴卡德</t>
+          <t>阿德莱德</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -11659,9 +12484,32 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
@@ -11669,16 +12517,13 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 19:06</t>
-        </is>
-      </c>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11688,22 +12533,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>美国职业大联盟</t>
+          <t>西班牙甲级联赛</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>多伦多</t>
+          <t>莱万特</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>迈国际</t>
+          <t>奥萨苏纳</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -11718,7 +12563,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>平-平</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -11731,9 +12576,32 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>大2.5</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
@@ -11741,16 +12609,17 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 19:06</t>
-        </is>
-      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>半全场平-平实际平-胜</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11760,22 +12629,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>西班牙甲级联赛</t>
+          <t>英格兰冠军联赛</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>马竞</t>
+          <t>赫尔城</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>塞尔塔</t>
+          <t>米尔沃尔</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -11790,7 +12659,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>平-负</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -11803,9 +12672,32 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
@@ -11813,16 +12705,17 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 19:06</t>
-        </is>
-      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>半全场平-负实际平-平</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11832,22 +12725,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>德国甲级联赛</t>
+          <t>法国甲级联赛</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>沃夫斯堡</t>
+          <t>朗斯</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>拜仁慕尼黑</t>
+          <t>南特</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -11862,7 +12755,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>胜-胜</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -11875,9 +12768,32 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>小2.5</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
@@ -11885,16 +12801,17 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 19:06</t>
-        </is>
-      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>半全场胜-胜实际平-胜</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11904,22 +12821,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>英格兰超级联赛</t>
+          <t>意大利甲级联赛</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>曼彻斯特城</t>
+          <t>都灵</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>布伦特</t>
+          <t>萨索洛</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -11934,7 +12851,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>平-平</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -11947,9 +12864,32 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>大2.5</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
@@ -11957,16 +12897,17 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 19:06</t>
-        </is>
-      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>半全场平-平实际平-胜</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11976,22 +12917,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>意大利甲级联赛</t>
+          <t>德国甲级联赛</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>拉齐奥</t>
+          <t>多特蒙德</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>国际米兰</t>
+          <t>法兰克福</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -12006,7 +12947,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>胜-胜</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -12019,9 +12960,32 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>胜-胜</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>大2.5</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
@@ -12029,18 +12993,491 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>复盘 @ 05-10 19:06</t>
-        </is>
-      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>半全场胜-胜命中</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>芬兰超级联赛</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>5007</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>库奥皮奥</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>塞伊奈约基</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>胜-胜</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>半全场胜-胜实际平-平</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>挪威超级联赛</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>5006</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>汉坎</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>瓦勒伦加</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>半全场平-平实际平-胜</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>瑞典超级联赛</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>埃夫斯堡</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>布鲁马波卡纳</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr"/>
+      <c r="V133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>德国乙级联赛</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>5004</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>凯泽斯劳滕</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>比勒费尔德</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>半全场平-负实际平-胜</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>德国乙级联赛</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>5003</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>帕德博恩</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>卡斯鲁厄</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr"/>
+      <c r="V135" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V50"/>
   <mergeCells count="4">
+    <mergeCell ref="T1:V1"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:N1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="T1:V1"/>
     <mergeCell ref="O1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Aii竞彩数据总表.xlsx
+++ b/Aii竞彩数据总表.xlsx
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU135"/>
+  <dimension ref="A1:AU149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10644,9 +10644,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -10677,8 +10674,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr"/>
-      <c r="V105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10736,9 +10731,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -10769,8 +10761,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr"/>
-      <c r="V106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -10828,9 +10818,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -10861,8 +10848,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr"/>
-      <c r="V107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -10920,9 +10905,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -10953,8 +10935,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr"/>
-      <c r="V108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11012,9 +10992,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -11045,8 +11022,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr"/>
-      <c r="V109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11104,9 +11079,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -11137,8 +11109,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr"/>
-      <c r="V110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11196,9 +11166,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -11229,8 +11196,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr"/>
-      <c r="V111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11288,9 +11253,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -11321,8 +11283,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr"/>
-      <c r="V112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11380,9 +11340,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -11413,8 +11370,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr"/>
-      <c r="V113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11472,9 +11427,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -11505,8 +11457,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr"/>
-      <c r="V114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11564,9 +11514,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -11597,8 +11544,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr"/>
-      <c r="V115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11656,9 +11601,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -11689,8 +11631,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr"/>
-      <c r="V116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -11748,9 +11688,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -11781,8 +11718,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr"/>
-      <c r="V117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -11840,9 +11775,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -11873,8 +11805,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr"/>
-      <c r="V118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11932,9 +11862,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -11965,8 +11892,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr"/>
-      <c r="V119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -12024,9 +11949,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -12057,8 +11979,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr"/>
-      <c r="V120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -12116,9 +12036,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -12149,8 +12066,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr"/>
-      <c r="V121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -12208,9 +12123,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -12241,8 +12153,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr"/>
-      <c r="V122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -12300,9 +12210,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -12333,8 +12240,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr"/>
-      <c r="V123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -12392,9 +12297,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -12425,8 +12327,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr"/>
-      <c r="V124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -12484,9 +12384,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -12517,8 +12414,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr"/>
-      <c r="V125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -12576,9 +12471,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -12614,7 +12506,6 @@
           <t>半全场平-平实际平-胜</t>
         </is>
       </c>
-      <c r="V126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -12672,9 +12563,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -12710,7 +12598,6 @@
           <t>半全场平-负实际平-平</t>
         </is>
       </c>
-      <c r="V127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -12768,9 +12655,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -12806,7 +12690,6 @@
           <t>半全场胜-胜实际平-胜</t>
         </is>
       </c>
-      <c r="V128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -12864,9 +12747,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -12902,7 +12782,6 @@
           <t>半全场平-平实际平-胜</t>
         </is>
       </c>
-      <c r="V129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -12960,9 +12839,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -12998,7 +12874,6 @@
           <t>半全场胜-胜命中</t>
         </is>
       </c>
-      <c r="V130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -13056,9 +12931,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -13094,7 +12966,6 @@
           <t>半全场胜-胜实际平-平</t>
         </is>
       </c>
-      <c r="V131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -13152,9 +13023,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -13190,7 +13058,6 @@
           <t>半全场平-平实际平-胜</t>
         </is>
       </c>
-      <c r="V132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -13248,9 +13115,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -13281,8 +13145,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr"/>
-      <c r="V133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -13340,9 +13202,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -13378,7 +13237,6 @@
           <t>半全场平-负实际平-胜</t>
         </is>
       </c>
-      <c r="V134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -13436,9 +13294,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -13469,15 +13324,1341 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr"/>
-      <c r="V135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>意大利甲级联赛</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>7005</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>维罗纳</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>科莫</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>让平/让负</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>部分正确</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>方向客胜命中; 大小球大2.5实际小2.5; 半全场负负实际平-负</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>日本职业联赛</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>7004</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>千叶市原</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>町田泽维</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>平负</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>让平/让负</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>部分正确</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>方向客胜命中; 大小球小2.5命中; 半全场平负实际平-负</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>日本职业联赛</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>7003</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>柏太阳神</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>川崎前锋</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>让平/让负</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>部分正确</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>方向主胜命中; 大小球小2.5命中; 半全场胜胜实际平-胜</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>日本职业联赛</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>7002</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>大阪钢巴</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>广岛三箭</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>平负</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>让平/让负</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>部分正确</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>方向客胜命中; 大小球小2.5命中; 半全场平负实际平-负</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>韩国职业联赛</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>7001</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>蔚山现代</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>富川FC</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>让平/让负</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>部分正确</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>方向主胜命中; 大小球小2.5命中; 半全场胜胜实际平-胜</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>西班牙甲级联赛</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>6030</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>皇家社会</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>贝蒂斯</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>平-平</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr"/>
+      <c r="V141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>意大利甲级联赛</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>6029</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>莱切</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>尤文图斯</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr"/>
+      <c r="V142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>法国乙级联赛</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>6028</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>阿纳西</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>罗德兹</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr"/>
+      <c r="V143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>沙特职业联赛</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>6027</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>迈季宽广</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>胡巴卡德</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr"/>
+      <c r="V144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>美国职业大联盟</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>6026</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>多伦多</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>迈国际</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr"/>
+      <c r="V145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>西班牙甲级联赛</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>6025</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>马竞</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>塞尔塔</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr"/>
+      <c r="V146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>德国甲级联赛</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>6024</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>沃夫斯堡</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>拜仁慕尼黑</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr"/>
+      <c r="V147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>英格兰超级联赛</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>6023</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>曼彻斯特城</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>布伦特</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>平-胜</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr"/>
+      <c r="V148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>意大利甲级联赛</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>6022</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>拉齐奥</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>国际米兰</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>平-负</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr"/>
+      <c r="V149" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V50"/>
   <mergeCells count="4">
-    <mergeCell ref="T1:V1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:N1"/>
+    <mergeCell ref="T1:V1"/>
     <mergeCell ref="O1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Aii竞彩数据总表.xlsx
+++ b/Aii竞彩数据总表.xlsx
@@ -13386,8 +13386,6 @@
           <t>4/10</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -13423,7 +13421,6 @@
           <t>方向客胜命中; 大小球大2.5实际小2.5; 半全场负负实际平-负</t>
         </is>
       </c>
-      <c r="V136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -13486,8 +13483,6 @@
           <t>2/10</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -13523,7 +13518,6 @@
           <t>方向客胜命中; 大小球小2.5命中; 半全场平负实际平-负</t>
         </is>
       </c>
-      <c r="V137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -13586,8 +13580,6 @@
           <t>2/10</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -13623,7 +13615,6 @@
           <t>方向主胜命中; 大小球小2.5命中; 半全场胜胜实际平-胜</t>
         </is>
       </c>
-      <c r="V138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -13686,8 +13677,6 @@
           <t>2/10</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -13723,7 +13712,6 @@
           <t>方向客胜命中; 大小球小2.5命中; 半全场平负实际平-负</t>
         </is>
       </c>
-      <c r="V139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -13786,8 +13774,6 @@
           <t>3/10</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -13823,7 +13809,6 @@
           <t>方向主胜命中; 大小球小2.5命中; 半全场胜胜实际平-胜</t>
         </is>
       </c>
-      <c r="V140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -13881,9 +13866,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -13914,8 +13896,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr"/>
-      <c r="V141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -13973,9 +13953,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -14006,8 +13983,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr"/>
-      <c r="V142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -14065,9 +14040,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -14098,8 +14070,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr"/>
-      <c r="V143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -14157,9 +14127,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -14190,8 +14157,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr"/>
-      <c r="V144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -14249,9 +14214,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr">
         <is>
           <t>2-4</t>
@@ -14282,8 +14244,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr"/>
-      <c r="V145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -14341,9 +14301,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -14374,8 +14331,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr"/>
-      <c r="V146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -14433,9 +14388,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -14466,8 +14418,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr"/>
-      <c r="V147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -14525,9 +14475,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -14558,8 +14505,6 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr"/>
-      <c r="V148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -14617,9 +14562,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -14650,15 +14592,13 @@
           <t>⏳</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr"/>
-      <c r="V149" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V50"/>
   <mergeCells count="4">
+    <mergeCell ref="T1:V1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:N1"/>
-    <mergeCell ref="T1:V1"/>
     <mergeCell ref="O1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Aii竞彩数据总表.xlsx
+++ b/Aii竞彩数据总表.xlsx
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU149"/>
+  <dimension ref="A1:AU159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14593,12 +14593,382 @@
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>沙特职业联赛</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>周一001</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>新未来SC</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>利雅得青年</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>数据来源：中国竞彩网（官方）· 11:38 | SP: 胜1.95/平3.62/负2.94 | 让球:-1 让胜3.9/让平3.75/让负1.65 | 开赛:2026-05-12 00:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>瑞超</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>周一002</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>天狼星</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>厄格里特</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>数据来源：中国竞彩网（官方）· 11:38 | SP: 胜未开/平未开/负未开 | 让球:-2 让胜2.38/让平4.1/让负2.15 | 开赛:2026-05-12 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>沙特职业联赛</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>周一003</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>布赖代合作</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>吉达国民</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>数据来源：中国竞彩网（官方）· 11:38 | SP: 胜3.5/平3.82/负1.72 | 让球:1 让胜1.89/让平3.6/让负3.1 | 开赛:2026-05-12 02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>意甲</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>周一004</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>那不勒斯</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>博洛尼亚</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>数据来源：中国竞彩网（官方）· 11:38 | SP: 胜1.41/平3.9/负6.1 | 让球:-1 让胜2.42/让平3.2/让负2.48 | 开赛:2026-05-12 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>英超</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>周一005</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>热刺</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>利兹联</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>数据来源：中国竞彩网（官方）· 11:38 | SP: 胜1.61/平3.7/负4.2 | 让球:-1 让胜3.0/让平3.35/让负2.01 | 开赛:2026-05-12 03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>英冠</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>周一006</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>米尔沃尔</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>赫尔城</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>数据来源：中国竞彩网（官方）· 11:38 | SP: 胜1.65/平3.42/负4.35 | 让球:-1 让胜3.0/让平3.45/让负1.98 | 开赛:2026-05-12 03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>周一007</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>巴列卡诺</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>赫罗纳</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>数据来源：中国竞彩网（官方）· 11:38 | SP: 胜2.22/平3.1/负2.81 | 让球:-1 让胜4.82/让平3.85/让负1.51 | 开赛:2026-05-12 03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>葡超</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>周一008</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>里奥阿维</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>里斯本</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>数据来源：中国竞彩网（官方）· 11:38 | SP: 胜未开/平未开/负未开 | 让球:2 让胜2.18/让平3.88/让负2.42 | 开赛:2026-05-12 03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>葡超</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>周一009</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>阿马多拉</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>法马利康</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>数据来源：中国竞彩网（官方）· 11:38 | SP: 胜3.3/平3.3/负1.91 | 让球:1 让胜1.7/让平3.55/让负3.85 | 开赛:2026-05-12 03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>葡超</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>周一010</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>本菲卡</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>布拉加</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>数据来源：中国竞彩网（官方）· 11:38 | SP: 胜1.28/平4.7/负7.4 | 让球:-1 让胜1.97/让平3.55/让负2.94 | 开赛:2026-05-12 03:15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:V50"/>
   <mergeCells count="4">
-    <mergeCell ref="T1:V1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:N1"/>
+    <mergeCell ref="T1:V1"/>
     <mergeCell ref="O1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Aii竞彩数据总表.xlsx
+++ b/Aii竞彩数据总表.xlsx
@@ -14624,6 +14624,39 @@
           <t>利雅得青年</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>1-0(1-1)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="M150" t="n">
+        <v>2</v>
+      </c>
       <c r="V150" t="inlineStr">
         <is>
           <t>数据来源：中国竞彩网（官方）· 11:38 | SP: 胜1.95/平3.62/负2.94 | 让球:-1 让胜3.9/让平3.75/让负1.65 | 开赛:2026-05-12 00:50</t>
@@ -14661,6 +14694,39 @@
           <t>厄格里特</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>1-0(1-1)</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="M151" t="n">
+        <v>2</v>
+      </c>
       <c r="V151" t="inlineStr">
         <is>
           <t>数据来源：中国竞彩网（官方）· 11:38 | SP: 胜未开/平未开/负未开 | 让球:-2 让胜2.38/让平4.1/让负2.15 | 开赛:2026-05-12 01:00</t>
@@ -14698,6 +14764,39 @@
           <t>吉达国民</t>
         </is>
       </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>0-1(1-1)</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>平负</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="M152" t="n">
+        <v>2</v>
+      </c>
       <c r="V152" t="inlineStr">
         <is>
           <t>数据来源：中国竞彩网（官方）· 11:38 | SP: 胜3.5/平3.82/负1.72 | 让球:1 让胜1.89/让平3.6/让负3.1 | 开赛:2026-05-12 02:00</t>
@@ -14735,6 +14834,39 @@
           <t>博洛尼亚</t>
         </is>
       </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>3-1(2-1)</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="M153" t="n">
+        <v>2</v>
+      </c>
       <c r="V153" t="inlineStr">
         <is>
           <t>数据来源：中国竞彩网（官方）· 11:38 | SP: 胜1.41/平3.9/负6.1 | 让球:-1 让胜2.42/让平3.2/让负2.48 | 开赛:2026-05-12 02:45</t>
@@ -14772,6 +14904,39 @@
           <t>利兹联</t>
         </is>
       </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>3-2(3-1)</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="M154" t="n">
+        <v>2</v>
+      </c>
       <c r="V154" t="inlineStr">
         <is>
           <t>数据来源：中国竞彩网（官方）· 11:38 | SP: 胜1.61/平3.7/负4.2 | 让球:-1 让胜3.0/让平3.35/让负2.01 | 开赛:2026-05-12 03:00</t>
@@ -14809,6 +14974,39 @@
           <t>赫尔城</t>
         </is>
       </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>2-1(2-2)</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="M155" t="n">
+        <v>2</v>
+      </c>
       <c r="V155" t="inlineStr">
         <is>
           <t>数据来源：中国竞彩网（官方）· 11:38 | SP: 胜1.65/平3.42/负4.35 | 让球:-1 让胜3.0/让平3.45/让负1.98 | 开赛:2026-05-12 03:00</t>
@@ -14846,6 +15044,39 @@
           <t>赫罗纳</t>
         </is>
       </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>2-1(1-2)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>负胜</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="M156" t="n">
+        <v>2</v>
+      </c>
       <c r="V156" t="inlineStr">
         <is>
           <t>数据来源：中国竞彩网（官方）· 11:38 | SP: 胜2.22/平3.1/负2.81 | 让球:-1 让胜4.82/让平3.85/让负1.51 | 开赛:2026-05-12 03:00</t>
@@ -14883,6 +15114,39 @@
           <t>里斯本</t>
         </is>
       </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>1-0(1-1)</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="M157" t="n">
+        <v>2</v>
+      </c>
       <c r="V157" t="inlineStr">
         <is>
           <t>数据来源：中国竞彩网（官方）· 11:38 | SP: 胜未开/平未开/负未开 | 让球:2 让胜2.18/让平3.88/让负2.42 | 开赛:2026-05-12 03:15</t>
@@ -14920,6 +15184,39 @@
           <t>法马利康</t>
         </is>
       </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>1-2(2-2)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="M158" t="n">
+        <v>2</v>
+      </c>
       <c r="V158" t="inlineStr">
         <is>
           <t>数据来源：中国竞彩网（官方）· 11:38 | SP: 胜3.3/平3.3/负1.91 | 让球:1 让胜1.7/让平3.55/让负3.85 | 开赛:2026-05-12 03:15</t>
@@ -14956,6 +15253,39 @@
         <is>
           <t>布拉加</t>
         </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>3-1(3-2)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="M159" t="n">
+        <v>2</v>
       </c>
       <c r="V159" t="inlineStr">
         <is>
@@ -14966,8 +15296,8 @@
   </sheetData>
   <autoFilter ref="A1:V50"/>
   <mergeCells count="4">
+    <mergeCell ref="G1:N1"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:N1"/>
     <mergeCell ref="T1:V1"/>
     <mergeCell ref="O1:S1"/>
   </mergeCells>

--- a/Aii竞彩数据总表.xlsx
+++ b/Aii竞彩数据总表.xlsx
@@ -669,8 +669,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU159"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:AU167"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
@@ -15293,12 +15293,404 @@
         </is>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>韩职</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>周二001</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>仁川联</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>浦项制铁</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M160" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N160" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O160" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>数据来源：中国竞彩网（官方）· 11:30 | SP: 胜2.49/平2.8/负2.7 | 让球:-1 让胜6.25/让平3.85/让负1.41 | 开赛:2026-05-12 18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>韩职</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>周二002</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>光州FC</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>首尔FC</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M161" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="N161" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="O161" t="n">
+        <v>1</v>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>数据来源：中国竞彩网（官方）· 11:30 | SP: 胜7.7/平4.15/负1.32 | 让球:1 让胜2.81/让平3.25/让负2.15 | 开赛:2026-05-12 18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>周二003</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>塞尔塔</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>莱万特</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M162" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N162" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>数据来源：中国竞彩网（官方）· 11:30 | SP: 胜1.67/平3.6/负3.95 | 让球:-1 让胜3.1/让平3.5/让负1.92 | 开赛:2026-05-12 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>沙职</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>周二004</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>利雅胜利</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>利雅新月</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M163" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N163" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>数据来源：中国竞彩网（官方）· 11:30 | SP: 胜1.98/平3.7/负2.82 | 让球:-1 让胜3.76/让平4.0/让负1.63 | 开赛:2026-05-12 02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>周二005</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>贝蒂斯</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>埃尔切</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M164" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N164" t="n">
+        <v>5</v>
+      </c>
+      <c r="O164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>数据来源：中国竞彩网（官方）· 11:30 | SP: 胜1.46/平4.1/负5.0 | 让球:-1 让胜2.5/让平3.4/让负2.3 | 开赛:2026-05-12 02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>法甲</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>周二006</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>圣旺红星</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>罗德兹</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M165" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N165" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O165" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>数据来源：中国竞彩网（官方）· 11:30 | SP: 胜1.95/平3.15/负3.35 | 让球:-1 让胜4.15/让平3.55/让负1.65 | 开赛:2026-05-12 02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>英冠</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>周二007</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>南安普敦</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>米堡</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M166" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="N166" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>数据来源：中国竞彩网（官方）· 11:30 | SP: 胜2.2/平3.22/负2.75 | 让球:-1 让胜4.6/让平4.08/让负1.5 | 开赛:2026-05-12 03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>周二008</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>奥萨苏纳</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>马竞</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="M167" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N167" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O167" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>数据来源：中国竞彩网（官方）· 11:30 | SP: 胜2.18/平3.3/负2.72 | 让球:-1 让胜4.65/让平3.9/让负1.52 | 开赛:2026-05-12 03:30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:V50"/>
   <mergeCells count="4">
+    <mergeCell ref="T1:V1"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:N1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="T1:V1"/>
     <mergeCell ref="O1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15313,7 +15705,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>

--- a/Aii竞彩数据总表.xlsx
+++ b/Aii竞彩数据总表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞彩数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计看板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="竞彩数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="统计看板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'竞彩数据'!$A$1:$V$50</definedName>
@@ -669,8 +669,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU167"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:AU177"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
@@ -15324,8 +15324,30 @@
           <t>浦项制铁</t>
         </is>
       </c>
-      <c r="L160" t="n">
-        <v>2.49</v>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
       </c>
       <c r="M160" t="n">
         <v>2.8</v>
@@ -15373,8 +15395,30 @@
           <t>首尔FC</t>
         </is>
       </c>
-      <c r="L161" t="n">
-        <v>7.7</v>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
       </c>
       <c r="M161" t="n">
         <v>4.15</v>
@@ -15422,8 +15466,30 @@
           <t>莱万特</t>
         </is>
       </c>
-      <c r="L162" t="n">
-        <v>1.67</v>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
       </c>
       <c r="M162" t="n">
         <v>3.6</v>
@@ -15471,8 +15537,30 @@
           <t>利雅新月</t>
         </is>
       </c>
-      <c r="L163" t="n">
-        <v>1.98</v>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
       </c>
       <c r="M163" t="n">
         <v>3.7</v>
@@ -15520,8 +15608,30 @@
           <t>埃尔切</t>
         </is>
       </c>
-      <c r="L164" t="n">
-        <v>1.46</v>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
       </c>
       <c r="M164" t="n">
         <v>4.1</v>
@@ -15569,8 +15679,30 @@
           <t>罗德兹</t>
         </is>
       </c>
-      <c r="L165" t="n">
-        <v>1.95</v>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
       </c>
       <c r="M165" t="n">
         <v>3.15</v>
@@ -15618,8 +15750,30 @@
           <t>米堡</t>
         </is>
       </c>
-      <c r="L166" t="n">
-        <v>2.2</v>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
       </c>
       <c r="M166" t="n">
         <v>3.22</v>
@@ -15667,8 +15821,30 @@
           <t>马竞</t>
         </is>
       </c>
-      <c r="L167" t="n">
-        <v>2.18</v>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
       </c>
       <c r="M167" t="n">
         <v>3.3</v>
@@ -15682,15 +15858,585 @@
       <c r="V167" t="inlineStr">
         <is>
           <t>数据来源：中国竞彩网（官方）· 11:30 | SP: 胜2.18/平3.3/负2.72 | 让球:-1 让胜4.65/让平3.9/让负1.52 | 开赛:2026-05-12 03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>日职</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>周三001</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>神户胜利船</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>京都不死鸟</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>韩职</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>周三002</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>富川FC</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>全北现代</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>周三003</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>比利亚雷亚尔</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>塞维利亚</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>周三004</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>西班牙人</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>毕尔巴鄂</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>法甲</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>周三005</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>布雷斯特</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>斯特拉斯堡</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>英超</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>周三006</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>曼城</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>水晶宫</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>意杯</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>周三007</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>拉齐奥</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>国米</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>法甲</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>周三008</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>朗斯</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>巴黎圣日耳曼</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>周三009</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>阿拉维斯</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>巴萨</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>周三010</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>赫塔菲</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>马略卡</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>3/10</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:V50"/>
   <mergeCells count="4">
-    <mergeCell ref="T1:V1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:N1"/>
+    <mergeCell ref="T1:V1"/>
     <mergeCell ref="O1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15705,7 +16451,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>

--- a/Aii竞彩数据总表.xlsx
+++ b/Aii竞彩数据总表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="竞彩数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="统计看板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞彩数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计看板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'竞彩数据'!$A$1:$V$50</definedName>
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU177"/>
+  <dimension ref="A1:AU189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16431,11 +16431,677 @@
         </is>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>日职</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>周三001</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>神户胜利</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>京都</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M178" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N178" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="O178" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr"/>
+      <c r="S178" t="inlineStr"/>
+      <c r="T178" t="inlineStr"/>
+      <c r="U178" t="inlineStr"/>
+      <c r="V178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>韩职</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>周三002</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>富川FC</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>全北现代</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M179" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="N179" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="O179" t="n">
+        <v>1</v>
+      </c>
+      <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr"/>
+      <c r="R179" t="inlineStr"/>
+      <c r="S179" t="inlineStr"/>
+      <c r="T179" t="inlineStr"/>
+      <c r="U179" t="inlineStr"/>
+      <c r="V179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>周三003</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>比利亚雷</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>塞维利亚</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M180" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="N180" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O180" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr"/>
+      <c r="S180" t="inlineStr"/>
+      <c r="T180" t="inlineStr"/>
+      <c r="U180" t="inlineStr"/>
+      <c r="V180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>周三004</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>西班牙人</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>毕尔巴鄂</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="M181" t="n">
+        <v>3</v>
+      </c>
+      <c r="N181" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O181" t="n">
+        <v>1</v>
+      </c>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="inlineStr"/>
+      <c r="S181" t="inlineStr"/>
+      <c r="T181" t="inlineStr"/>
+      <c r="U181" t="inlineStr"/>
+      <c r="V181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>法甲</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>周三005</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>布雷斯特</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>斯特拉斯</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M182" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N182" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O182" t="n">
+        <v>1</v>
+      </c>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr"/>
+      <c r="S182" t="inlineStr"/>
+      <c r="T182" t="inlineStr"/>
+      <c r="U182" t="inlineStr"/>
+      <c r="V182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>英超</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>周三006</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>曼城</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>水晶宫</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr"/>
+      <c r="S183" t="inlineStr"/>
+      <c r="T183" t="inlineStr"/>
+      <c r="U183" t="inlineStr"/>
+      <c r="V183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>意大利杯</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>周三007</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>拉齐奥</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>国际米兰</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M184" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N184" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O184" t="n">
+        <v>1</v>
+      </c>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr"/>
+      <c r="S184" t="inlineStr"/>
+      <c r="T184" t="inlineStr"/>
+      <c r="U184" t="inlineStr"/>
+      <c r="V184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>法甲</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>周三008</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>朗斯</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>巴黎圣曼</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M185" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N185" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="O185" t="n">
+        <v>1</v>
+      </c>
+      <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr"/>
+      <c r="S185" t="inlineStr"/>
+      <c r="T185" t="inlineStr"/>
+      <c r="U185" t="inlineStr"/>
+      <c r="V185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>周三009</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>阿拉维斯</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>巴萨</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="M186" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N186" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="O186" t="n">
+        <v>1</v>
+      </c>
+      <c r="P186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="inlineStr"/>
+      <c r="S186" t="inlineStr"/>
+      <c r="T186" t="inlineStr"/>
+      <c r="U186" t="inlineStr"/>
+      <c r="V186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>周三010</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>赫塔费</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>马洛卡</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M187" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="N187" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O187" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr"/>
+      <c r="S187" t="inlineStr"/>
+      <c r="T187" t="inlineStr"/>
+      <c r="U187" t="inlineStr"/>
+      <c r="V187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>美职</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>周三011</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>辛辛那提</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>迈国际</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M188" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N188" t="n">
+        <v>2</v>
+      </c>
+      <c r="O188" t="n">
+        <v>1</v>
+      </c>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr"/>
+      <c r="S188" t="inlineStr"/>
+      <c r="T188" t="inlineStr"/>
+      <c r="U188" t="inlineStr"/>
+      <c r="V188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>美职</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>周三012</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>西雅图</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>圣何塞</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M189" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N189" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O189" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr"/>
+      <c r="S189" t="inlineStr"/>
+      <c r="T189" t="inlineStr"/>
+      <c r="U189" t="inlineStr"/>
+      <c r="V189" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:V50"/>
   <mergeCells count="4">
+    <mergeCell ref="G1:N1"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:N1"/>
     <mergeCell ref="T1:V1"/>
     <mergeCell ref="O1:S1"/>
   </mergeCells>

--- a/Aii竞彩数据总表.xlsx
+++ b/Aii竞彩数据总表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞彩数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计看板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="竞彩数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="统计看板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'竞彩数据'!$A$1:$V$50</definedName>
@@ -16462,11 +16462,31 @@
           <t>京都</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>备选:平胜</t>
+        </is>
+      </c>
       <c r="L178" t="n">
         <v>1.61</v>
       </c>
@@ -16479,13 +16499,6 @@
       <c r="O178" t="n">
         <v>-1</v>
       </c>
-      <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="inlineStr"/>
-      <c r="R178" t="inlineStr"/>
-      <c r="S178" t="inlineStr"/>
-      <c r="T178" t="inlineStr"/>
-      <c r="U178" t="inlineStr"/>
-      <c r="V178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -16518,11 +16531,31 @@
           <t>全北现代</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>备选:平负</t>
+        </is>
+      </c>
       <c r="L179" t="n">
         <v>4.7</v>
       </c>
@@ -16535,13 +16568,6 @@
       <c r="O179" t="n">
         <v>1</v>
       </c>
-      <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="inlineStr"/>
-      <c r="R179" t="inlineStr"/>
-      <c r="S179" t="inlineStr"/>
-      <c r="T179" t="inlineStr"/>
-      <c r="U179" t="inlineStr"/>
-      <c r="V179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -16574,11 +16600,31 @@
           <t>塞维利亚</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>备选:负胜</t>
+        </is>
+      </c>
       <c r="L180" t="n">
         <v>1.92</v>
       </c>
@@ -16591,13 +16637,6 @@
       <c r="O180" t="n">
         <v>-1</v>
       </c>
-      <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="inlineStr"/>
-      <c r="R180" t="inlineStr"/>
-      <c r="S180" t="inlineStr"/>
-      <c r="T180" t="inlineStr"/>
-      <c r="U180" t="inlineStr"/>
-      <c r="V180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -16630,11 +16669,31 @@
           <t>毕尔巴鄂</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>备选:平胜</t>
+        </is>
+      </c>
       <c r="L181" t="n">
         <v>2.64</v>
       </c>
@@ -16647,13 +16706,6 @@
       <c r="O181" t="n">
         <v>1</v>
       </c>
-      <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="inlineStr"/>
-      <c r="R181" t="inlineStr"/>
-      <c r="S181" t="inlineStr"/>
-      <c r="T181" t="inlineStr"/>
-      <c r="U181" t="inlineStr"/>
-      <c r="V181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -16686,11 +16738,31 @@
           <t>斯特拉斯</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>备选:负胜</t>
+        </is>
+      </c>
       <c r="L182" t="n">
         <v>2.6</v>
       </c>
@@ -16703,13 +16775,6 @@
       <c r="O182" t="n">
         <v>1</v>
       </c>
-      <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="inlineStr"/>
-      <c r="R182" t="inlineStr"/>
-      <c r="S182" t="inlineStr"/>
-      <c r="T182" t="inlineStr"/>
-      <c r="U182" t="inlineStr"/>
-      <c r="V182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -16742,24 +16807,39 @@
           <t>水晶宫</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>备选:平胜</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
       <c r="O183" t="n">
         <v>-2</v>
       </c>
-      <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr"/>
-      <c r="R183" t="inlineStr"/>
-      <c r="S183" t="inlineStr"/>
-      <c r="T183" t="inlineStr"/>
-      <c r="U183" t="inlineStr"/>
-      <c r="V183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -16792,11 +16872,31 @@
           <t>国际米兰</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>备选:平负</t>
+        </is>
+      </c>
       <c r="L184" t="n">
         <v>5.2</v>
       </c>
@@ -16809,13 +16909,6 @@
       <c r="O184" t="n">
         <v>1</v>
       </c>
-      <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="inlineStr"/>
-      <c r="R184" t="inlineStr"/>
-      <c r="S184" t="inlineStr"/>
-      <c r="T184" t="inlineStr"/>
-      <c r="U184" t="inlineStr"/>
-      <c r="V184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -16848,11 +16941,31 @@
           <t>巴黎圣曼</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>备选:平负</t>
+        </is>
+      </c>
       <c r="L185" t="n">
         <v>3.05</v>
       </c>
@@ -16865,13 +16978,6 @@
       <c r="O185" t="n">
         <v>1</v>
       </c>
-      <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="inlineStr"/>
-      <c r="R185" t="inlineStr"/>
-      <c r="S185" t="inlineStr"/>
-      <c r="T185" t="inlineStr"/>
-      <c r="U185" t="inlineStr"/>
-      <c r="V185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -16904,11 +17010,31 @@
           <t>巴萨</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>备选:平负</t>
+        </is>
+      </c>
       <c r="L186" t="n">
         <v>2.91</v>
       </c>
@@ -16921,13 +17047,6 @@
       <c r="O186" t="n">
         <v>1</v>
       </c>
-      <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="inlineStr"/>
-      <c r="R186" t="inlineStr"/>
-      <c r="S186" t="inlineStr"/>
-      <c r="T186" t="inlineStr"/>
-      <c r="U186" t="inlineStr"/>
-      <c r="V186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -16960,11 +17079,31 @@
           <t>马洛卡</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>备选:平胜</t>
+        </is>
+      </c>
       <c r="L187" t="n">
         <v>2.05</v>
       </c>
@@ -16977,13 +17116,6 @@
       <c r="O187" t="n">
         <v>-1</v>
       </c>
-      <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="inlineStr"/>
-      <c r="R187" t="inlineStr"/>
-      <c r="S187" t="inlineStr"/>
-      <c r="T187" t="inlineStr"/>
-      <c r="U187" t="inlineStr"/>
-      <c r="V187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -17016,11 +17148,31 @@
           <t>迈国际</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>备选:平负</t>
+        </is>
+      </c>
       <c r="L188" t="n">
         <v>2.66</v>
       </c>
@@ -17033,13 +17185,6 @@
       <c r="O188" t="n">
         <v>1</v>
       </c>
-      <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr"/>
-      <c r="R188" t="inlineStr"/>
-      <c r="S188" t="inlineStr"/>
-      <c r="T188" t="inlineStr"/>
-      <c r="U188" t="inlineStr"/>
-      <c r="V188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -17072,11 +17217,31 @@
           <t>圣何塞</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>备选:平胜</t>
+        </is>
+      </c>
       <c r="L189" t="n">
         <v>1.7</v>
       </c>
@@ -17089,20 +17254,13 @@
       <c r="O189" t="n">
         <v>-1</v>
       </c>
-      <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="inlineStr"/>
-      <c r="R189" t="inlineStr"/>
-      <c r="S189" t="inlineStr"/>
-      <c r="T189" t="inlineStr"/>
-      <c r="U189" t="inlineStr"/>
-      <c r="V189" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V50"/>
   <mergeCells count="4">
+    <mergeCell ref="T1:V1"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:N1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="T1:V1"/>
     <mergeCell ref="O1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Aii竞彩数据总表.xlsx
+++ b/Aii竞彩数据总表.xlsx
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU189"/>
+  <dimension ref="A1:AU211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17255,12 +17255,1552 @@
         <v>-1</v>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>澳超</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>周六005</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>纽喷气机</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>悉尼FC</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr"/>
+      <c r="S190" t="inlineStr"/>
+      <c r="T190" t="inlineStr"/>
+      <c r="U190" t="inlineStr"/>
+      <c r="V190" t="inlineStr"/>
+      <c r="W190" t="inlineStr"/>
+      <c r="X190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>韩职</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>周六006</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>仁川联</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>光州FC</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="inlineStr"/>
+      <c r="S191" t="inlineStr"/>
+      <c r="T191" t="inlineStr"/>
+      <c r="U191" t="inlineStr"/>
+      <c r="V191" t="inlineStr"/>
+      <c r="W191" t="inlineStr"/>
+      <c r="X191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>挪超</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>周六008</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>布兰</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>奥斯KFUM</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr"/>
+      <c r="S192" t="inlineStr"/>
+      <c r="T192" t="inlineStr"/>
+      <c r="U192" t="inlineStr"/>
+      <c r="V192" t="inlineStr"/>
+      <c r="W192" t="inlineStr"/>
+      <c r="X192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>瑞超</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>周六009</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>哈尔姆斯</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>埃夫斯堡</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr"/>
+      <c r="R193" t="inlineStr"/>
+      <c r="S193" t="inlineStr"/>
+      <c r="T193" t="inlineStr"/>
+      <c r="U193" t="inlineStr"/>
+      <c r="V193" t="inlineStr"/>
+      <c r="W193" t="inlineStr"/>
+      <c r="X193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>周六011</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>勒沃库森</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>汉堡</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr"/>
+      <c r="R194" t="inlineStr"/>
+      <c r="S194" t="inlineStr"/>
+      <c r="T194" t="inlineStr"/>
+      <c r="U194" t="inlineStr"/>
+      <c r="V194" t="inlineStr"/>
+      <c r="W194" t="inlineStr"/>
+      <c r="X194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>周六012</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>拜仁</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>科隆</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
+      <c r="R195" t="inlineStr"/>
+      <c r="S195" t="inlineStr"/>
+      <c r="T195" t="inlineStr"/>
+      <c r="U195" t="inlineStr"/>
+      <c r="V195" t="inlineStr"/>
+      <c r="W195" t="inlineStr"/>
+      <c r="X195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>周六013</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>海登海姆</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>美因茨</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr"/>
+      <c r="S196" t="inlineStr"/>
+      <c r="T196" t="inlineStr"/>
+      <c r="U196" t="inlineStr"/>
+      <c r="V196" t="inlineStr"/>
+      <c r="W196" t="inlineStr"/>
+      <c r="X196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>周六014</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>圣保利</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>沃夫斯堡</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr"/>
+      <c r="R197" t="inlineStr"/>
+      <c r="S197" t="inlineStr"/>
+      <c r="T197" t="inlineStr"/>
+      <c r="U197" t="inlineStr"/>
+      <c r="V197" t="inlineStr"/>
+      <c r="W197" t="inlineStr"/>
+      <c r="X197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>周六015</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>柏林联合</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>奥格斯堡</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr"/>
+      <c r="S198" t="inlineStr"/>
+      <c r="T198" t="inlineStr"/>
+      <c r="U198" t="inlineStr"/>
+      <c r="V198" t="inlineStr"/>
+      <c r="W198" t="inlineStr"/>
+      <c r="X198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>周六016</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>法兰克福</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>斯图加特</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>平负</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr"/>
+      <c r="R199" t="inlineStr"/>
+      <c r="S199" t="inlineStr"/>
+      <c r="T199" t="inlineStr"/>
+      <c r="U199" t="inlineStr"/>
+      <c r="V199" t="inlineStr"/>
+      <c r="W199" t="inlineStr"/>
+      <c r="X199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>周六017</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>不来梅</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>多特蒙德</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr"/>
+      <c r="S200" t="inlineStr"/>
+      <c r="T200" t="inlineStr"/>
+      <c r="U200" t="inlineStr"/>
+      <c r="V200" t="inlineStr"/>
+      <c r="W200" t="inlineStr"/>
+      <c r="X200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>周六018</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>门兴</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>霍芬海姆</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr"/>
+      <c r="S201" t="inlineStr"/>
+      <c r="T201" t="inlineStr"/>
+      <c r="U201" t="inlineStr"/>
+      <c r="V201" t="inlineStr"/>
+      <c r="W201" t="inlineStr"/>
+      <c r="X201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>周六019</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>弗赖堡</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>莱红牛</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr"/>
+      <c r="S202" t="inlineStr"/>
+      <c r="T202" t="inlineStr"/>
+      <c r="U202" t="inlineStr"/>
+      <c r="V202" t="inlineStr"/>
+      <c r="W202" t="inlineStr"/>
+      <c r="X202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>英足总杯</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>周六020</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>切尔西</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>曼城</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr"/>
+      <c r="S203" t="inlineStr"/>
+      <c r="T203" t="inlineStr"/>
+      <c r="U203" t="inlineStr"/>
+      <c r="V203" t="inlineStr"/>
+      <c r="W203" t="inlineStr"/>
+      <c r="X203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>挪超</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>周六021</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>博德闪耀</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>特罗姆瑟</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="inlineStr"/>
+      <c r="S204" t="inlineStr"/>
+      <c r="T204" t="inlineStr"/>
+      <c r="U204" t="inlineStr"/>
+      <c r="V204" t="inlineStr"/>
+      <c r="W204" t="inlineStr"/>
+      <c r="X204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>葡超</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>周六024</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>布拉加</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>阿马多拉</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr"/>
+      <c r="S205" t="inlineStr"/>
+      <c r="T205" t="inlineStr"/>
+      <c r="U205" t="inlineStr"/>
+      <c r="V205" t="inlineStr"/>
+      <c r="W205" t="inlineStr"/>
+      <c r="X205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>亚冠乙</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>周六025</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>利雅胜利</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>大阪钢巴</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr"/>
+      <c r="S206" t="inlineStr"/>
+      <c r="T206" t="inlineStr"/>
+      <c r="U206" t="inlineStr"/>
+      <c r="V206" t="inlineStr"/>
+      <c r="W206" t="inlineStr"/>
+      <c r="X206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>沙职</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>周六026</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>吉达国民</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>拉斯永恒</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr"/>
+      <c r="S207" t="inlineStr"/>
+      <c r="T207" t="inlineStr"/>
+      <c r="U207" t="inlineStr"/>
+      <c r="V207" t="inlineStr"/>
+      <c r="W207" t="inlineStr"/>
+      <c r="X207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>葡超</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>周六027</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>里斯本</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>吉维森特</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr"/>
+      <c r="S208" t="inlineStr"/>
+      <c r="T208" t="inlineStr"/>
+      <c r="U208" t="inlineStr"/>
+      <c r="V208" t="inlineStr"/>
+      <c r="W208" t="inlineStr"/>
+      <c r="X208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>葡超</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>周六028</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>埃斯托里</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>本菲卡</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>大2.5</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="inlineStr"/>
+      <c r="S209" t="inlineStr"/>
+      <c r="T209" t="inlineStr"/>
+      <c r="U209" t="inlineStr"/>
+      <c r="V209" t="inlineStr"/>
+      <c r="W209" t="inlineStr"/>
+      <c r="X209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>美职</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>周六029</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>纽约红牛</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>纽约城</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="inlineStr"/>
+      <c r="S210" t="inlineStr"/>
+      <c r="T210" t="inlineStr"/>
+      <c r="U210" t="inlineStr"/>
+      <c r="V210" t="inlineStr"/>
+      <c r="W210" t="inlineStr"/>
+      <c r="X210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>美职</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>周六030</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>新英格兰</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>明尼苏达</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr"/>
+      <c r="R211" t="inlineStr"/>
+      <c r="S211" t="inlineStr"/>
+      <c r="T211" t="inlineStr"/>
+      <c r="U211" t="inlineStr"/>
+      <c r="V211" t="inlineStr"/>
+      <c r="W211" t="inlineStr"/>
+      <c r="X211" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:V50"/>
   <mergeCells count="4">
-    <mergeCell ref="T1:V1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:N1"/>
+    <mergeCell ref="T1:V1"/>
     <mergeCell ref="O1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Aii竞彩数据总表.xlsx
+++ b/Aii竞彩数据总表.xlsx
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU211"/>
+  <dimension ref="A1:AU233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17306,24 +17306,11 @@
           <t>小2.5</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
           <t>2/10</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr"/>
-      <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="inlineStr"/>
-      <c r="R190" t="inlineStr"/>
-      <c r="S190" t="inlineStr"/>
-      <c r="T190" t="inlineStr"/>
-      <c r="U190" t="inlineStr"/>
-      <c r="V190" t="inlineStr"/>
-      <c r="W190" t="inlineStr"/>
-      <c r="X190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -17376,24 +17363,11 @@
           <t>小2.5</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
           <t>3/10</t>
         </is>
       </c>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
-      <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr"/>
-      <c r="R191" t="inlineStr"/>
-      <c r="S191" t="inlineStr"/>
-      <c r="T191" t="inlineStr"/>
-      <c r="U191" t="inlineStr"/>
-      <c r="V191" t="inlineStr"/>
-      <c r="W191" t="inlineStr"/>
-      <c r="X191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -17446,24 +17420,11 @@
           <t>小2.5</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
           <t>3/10</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
-      <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr"/>
-      <c r="R192" t="inlineStr"/>
-      <c r="S192" t="inlineStr"/>
-      <c r="T192" t="inlineStr"/>
-      <c r="U192" t="inlineStr"/>
-      <c r="V192" t="inlineStr"/>
-      <c r="W192" t="inlineStr"/>
-      <c r="X192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -17516,24 +17477,11 @@
           <t>小2.5</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
           <t>3/10</t>
         </is>
       </c>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr"/>
-      <c r="P193" t="inlineStr"/>
-      <c r="Q193" t="inlineStr"/>
-      <c r="R193" t="inlineStr"/>
-      <c r="S193" t="inlineStr"/>
-      <c r="T193" t="inlineStr"/>
-      <c r="U193" t="inlineStr"/>
-      <c r="V193" t="inlineStr"/>
-      <c r="W193" t="inlineStr"/>
-      <c r="X193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -17586,24 +17534,11 @@
           <t>大2.5</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
           <t>4/10</t>
         </is>
       </c>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr"/>
-      <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="inlineStr"/>
-      <c r="R194" t="inlineStr"/>
-      <c r="S194" t="inlineStr"/>
-      <c r="T194" t="inlineStr"/>
-      <c r="U194" t="inlineStr"/>
-      <c r="V194" t="inlineStr"/>
-      <c r="W194" t="inlineStr"/>
-      <c r="X194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -17656,24 +17591,11 @@
           <t>小2.5</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
           <t>4/10</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
-      <c r="O195" t="inlineStr"/>
-      <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="inlineStr"/>
-      <c r="R195" t="inlineStr"/>
-      <c r="S195" t="inlineStr"/>
-      <c r="T195" t="inlineStr"/>
-      <c r="U195" t="inlineStr"/>
-      <c r="V195" t="inlineStr"/>
-      <c r="W195" t="inlineStr"/>
-      <c r="X195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -17726,24 +17648,11 @@
           <t>大2.5</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
           <t>4/10</t>
         </is>
       </c>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
-      <c r="O196" t="inlineStr"/>
-      <c r="P196" t="inlineStr"/>
-      <c r="Q196" t="inlineStr"/>
-      <c r="R196" t="inlineStr"/>
-      <c r="S196" t="inlineStr"/>
-      <c r="T196" t="inlineStr"/>
-      <c r="U196" t="inlineStr"/>
-      <c r="V196" t="inlineStr"/>
-      <c r="W196" t="inlineStr"/>
-      <c r="X196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -17796,24 +17705,11 @@
           <t>大2.5</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
           <t>3/10</t>
         </is>
       </c>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
-      <c r="O197" t="inlineStr"/>
-      <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="inlineStr"/>
-      <c r="R197" t="inlineStr"/>
-      <c r="S197" t="inlineStr"/>
-      <c r="T197" t="inlineStr"/>
-      <c r="U197" t="inlineStr"/>
-      <c r="V197" t="inlineStr"/>
-      <c r="W197" t="inlineStr"/>
-      <c r="X197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -17866,24 +17762,11 @@
           <t>大2.5</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
           <t>3/10</t>
         </is>
       </c>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
-      <c r="O198" t="inlineStr"/>
-      <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="inlineStr"/>
-      <c r="R198" t="inlineStr"/>
-      <c r="S198" t="inlineStr"/>
-      <c r="T198" t="inlineStr"/>
-      <c r="U198" t="inlineStr"/>
-      <c r="V198" t="inlineStr"/>
-      <c r="W198" t="inlineStr"/>
-      <c r="X198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -17936,24 +17819,11 @@
           <t>小2.5</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
           <t>4/10</t>
         </is>
       </c>
-      <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
-      <c r="O199" t="inlineStr"/>
-      <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="inlineStr"/>
-      <c r="R199" t="inlineStr"/>
-      <c r="S199" t="inlineStr"/>
-      <c r="T199" t="inlineStr"/>
-      <c r="U199" t="inlineStr"/>
-      <c r="V199" t="inlineStr"/>
-      <c r="W199" t="inlineStr"/>
-      <c r="X199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -18006,24 +17876,11 @@
           <t>大2.5</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
           <t>4/10</t>
         </is>
       </c>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
-      <c r="O200" t="inlineStr"/>
-      <c r="P200" t="inlineStr"/>
-      <c r="Q200" t="inlineStr"/>
-      <c r="R200" t="inlineStr"/>
-      <c r="S200" t="inlineStr"/>
-      <c r="T200" t="inlineStr"/>
-      <c r="U200" t="inlineStr"/>
-      <c r="V200" t="inlineStr"/>
-      <c r="W200" t="inlineStr"/>
-      <c r="X200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -18076,24 +17933,11 @@
           <t>大2.5</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
           <t>4/10</t>
         </is>
       </c>
-      <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
-      <c r="O201" t="inlineStr"/>
-      <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="inlineStr"/>
-      <c r="R201" t="inlineStr"/>
-      <c r="S201" t="inlineStr"/>
-      <c r="T201" t="inlineStr"/>
-      <c r="U201" t="inlineStr"/>
-      <c r="V201" t="inlineStr"/>
-      <c r="W201" t="inlineStr"/>
-      <c r="X201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -18146,24 +17990,11 @@
           <t>大2.5</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr">
         <is>
           <t>4/10</t>
         </is>
       </c>
-      <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
-      <c r="O202" t="inlineStr"/>
-      <c r="P202" t="inlineStr"/>
-      <c r="Q202" t="inlineStr"/>
-      <c r="R202" t="inlineStr"/>
-      <c r="S202" t="inlineStr"/>
-      <c r="T202" t="inlineStr"/>
-      <c r="U202" t="inlineStr"/>
-      <c r="V202" t="inlineStr"/>
-      <c r="W202" t="inlineStr"/>
-      <c r="X202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -18216,24 +18047,11 @@
           <t>大2.5</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
           <t>1/10</t>
         </is>
       </c>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr"/>
-      <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="inlineStr"/>
-      <c r="R203" t="inlineStr"/>
-      <c r="S203" t="inlineStr"/>
-      <c r="T203" t="inlineStr"/>
-      <c r="U203" t="inlineStr"/>
-      <c r="V203" t="inlineStr"/>
-      <c r="W203" t="inlineStr"/>
-      <c r="X203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -18286,24 +18104,11 @@
           <t>小2.5</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
           <t>3/10</t>
         </is>
       </c>
-      <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
-      <c r="O204" t="inlineStr"/>
-      <c r="P204" t="inlineStr"/>
-      <c r="Q204" t="inlineStr"/>
-      <c r="R204" t="inlineStr"/>
-      <c r="S204" t="inlineStr"/>
-      <c r="T204" t="inlineStr"/>
-      <c r="U204" t="inlineStr"/>
-      <c r="V204" t="inlineStr"/>
-      <c r="W204" t="inlineStr"/>
-      <c r="X204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -18356,24 +18161,11 @@
           <t>大2.5</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
           <t>4/10</t>
         </is>
       </c>
-      <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
-      <c r="O205" t="inlineStr"/>
-      <c r="P205" t="inlineStr"/>
-      <c r="Q205" t="inlineStr"/>
-      <c r="R205" t="inlineStr"/>
-      <c r="S205" t="inlineStr"/>
-      <c r="T205" t="inlineStr"/>
-      <c r="U205" t="inlineStr"/>
-      <c r="V205" t="inlineStr"/>
-      <c r="W205" t="inlineStr"/>
-      <c r="X205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -18426,24 +18218,11 @@
           <t>小2.5</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
           <t>1/10</t>
         </is>
       </c>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
-      <c r="O206" t="inlineStr"/>
-      <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="inlineStr"/>
-      <c r="R206" t="inlineStr"/>
-      <c r="S206" t="inlineStr"/>
-      <c r="T206" t="inlineStr"/>
-      <c r="U206" t="inlineStr"/>
-      <c r="V206" t="inlineStr"/>
-      <c r="W206" t="inlineStr"/>
-      <c r="X206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -18496,24 +18275,11 @@
           <t>小2.5</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
           <t>1/10</t>
         </is>
       </c>
-      <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
-      <c r="O207" t="inlineStr"/>
-      <c r="P207" t="inlineStr"/>
-      <c r="Q207" t="inlineStr"/>
-      <c r="R207" t="inlineStr"/>
-      <c r="S207" t="inlineStr"/>
-      <c r="T207" t="inlineStr"/>
-      <c r="U207" t="inlineStr"/>
-      <c r="V207" t="inlineStr"/>
-      <c r="W207" t="inlineStr"/>
-      <c r="X207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -18566,24 +18332,11 @@
           <t>小2.5</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
           <t>2/10</t>
         </is>
       </c>
-      <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
-      <c r="O208" t="inlineStr"/>
-      <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="inlineStr"/>
-      <c r="R208" t="inlineStr"/>
-      <c r="S208" t="inlineStr"/>
-      <c r="T208" t="inlineStr"/>
-      <c r="U208" t="inlineStr"/>
-      <c r="V208" t="inlineStr"/>
-      <c r="W208" t="inlineStr"/>
-      <c r="X208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -18636,24 +18389,11 @@
           <t>大2.5</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
           <t>4/10</t>
         </is>
       </c>
-      <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
-      <c r="O209" t="inlineStr"/>
-      <c r="P209" t="inlineStr"/>
-      <c r="Q209" t="inlineStr"/>
-      <c r="R209" t="inlineStr"/>
-      <c r="S209" t="inlineStr"/>
-      <c r="T209" t="inlineStr"/>
-      <c r="U209" t="inlineStr"/>
-      <c r="V209" t="inlineStr"/>
-      <c r="W209" t="inlineStr"/>
-      <c r="X209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -18706,24 +18446,11 @@
           <t>小2.5</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
           <t>1/10</t>
         </is>
       </c>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
-      <c r="O210" t="inlineStr"/>
-      <c r="P210" t="inlineStr"/>
-      <c r="Q210" t="inlineStr"/>
-      <c r="R210" t="inlineStr"/>
-      <c r="S210" t="inlineStr"/>
-      <c r="T210" t="inlineStr"/>
-      <c r="U210" t="inlineStr"/>
-      <c r="V210" t="inlineStr"/>
-      <c r="W210" t="inlineStr"/>
-      <c r="X210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -18776,24 +18503,1045 @@
           <t>小2.5</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
           <t>1/10</t>
         </is>
       </c>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
-      <c r="O211" t="inlineStr"/>
-      <c r="P211" t="inlineStr"/>
-      <c r="Q211" t="inlineStr"/>
-      <c r="R211" t="inlineStr"/>
-      <c r="S211" t="inlineStr"/>
-      <c r="T211" t="inlineStr"/>
-      <c r="U211" t="inlineStr"/>
-      <c r="V211" t="inlineStr"/>
-      <c r="W211" t="inlineStr"/>
-      <c r="X211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>日职</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>周六001</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>水户蜀葵</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>东京绿茵</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>日职</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>周六002</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>浦和红钻</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>东京FC</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>韩职</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>周六003</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>大田市民</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>首尔FC</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>日职</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>周六004</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>横滨水手</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>柏太阳神</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>芬超</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>周六007</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>赫尔辛基</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>坦山猫</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>瑞超</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>周六010</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>盖斯</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>代格福什</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>芬超</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>周六022</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>赫尔火花</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>雅罗</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>竞彩</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>芬超</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>周六023</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>AC奥卢</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>TPS图尔</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>小2.5</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>14场</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>英足总杯</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>切尔西</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>曼彻斯特城</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>客胜/平局</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>14场</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>拜仁慕尼黑</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>科隆</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>14场</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>弗赖堡</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>莱比锡红牛</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>4.3/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>14场</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>法兰克福</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>斯图加特</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>客胜/平局</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>14场</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>海登海姆</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>美因茨</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>14场</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>勒沃库森</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>汉堡</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>14场</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>门兴格拉德巴赫</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>霍芬海姆</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>客胜/平局</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>14场</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>圣保利</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>沃尔夫斯堡</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>4.2/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>14场</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>柏林联合</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>奥格斯堡</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>14场</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>云达不来梅</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>多特蒙德</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>14场</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>葡超</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>布拉加</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>阿马多拉</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>14场</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>葡超</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>埃斯托里尔</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>本菲卡</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>14场</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>葡超</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>里斯本竞技</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>吉维森特</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>14场</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>挪超</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>莫尔德</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>克里斯蒂安松</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>2.4/10</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:V50"/>
